--- a/data/hydroExample/Power_ThermalGen.xlsx
+++ b/data/hydroExample/Power_ThermalGen.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768921A2-DF0C-478C-A16F-326FD6706BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3797F0-22C4-4EBA-8C49-014EF1246937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario_2016" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -114,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="210">
   <si>
     <t>Power - Thermal Generators</t>
   </si>
@@ -404,100 +417,346 @@
     <t>Nuclear</t>
   </si>
   <si>
-    <t>Node_7</t>
-  </si>
-  <si>
-    <t>TestPackage1</t>
-  </si>
-  <si>
-    <t>TestSource1</t>
-  </si>
-  <si>
-    <t>DomesticCoal_Anthracite</t>
-  </si>
-  <si>
-    <t>Coal</t>
-  </si>
-  <si>
-    <t>Node_2</t>
-  </si>
-  <si>
-    <t>BrownLignite</t>
-  </si>
-  <si>
-    <t>Node_3</t>
-  </si>
-  <si>
-    <t>ImportedCoal_SubBituminous</t>
-  </si>
-  <si>
-    <t>Node_4</t>
-  </si>
-  <si>
-    <t>ImportedCoal_Bituminous</t>
-  </si>
-  <si>
-    <t>Node_1</t>
-  </si>
-  <si>
-    <t>CCGT_1</t>
-  </si>
-  <si>
     <t>Gas</t>
   </si>
   <si>
-    <t>Node_6</t>
-  </si>
-  <si>
-    <t>CCGT_2</t>
-  </si>
-  <si>
-    <t>CCGT_3</t>
-  </si>
-  <si>
-    <t>TestSource1-Manual2.1</t>
-  </si>
-  <si>
-    <t>CCGT_4</t>
-  </si>
-  <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>CCGT_5</t>
-  </si>
-  <si>
-    <t>CCGT_6</t>
-  </si>
-  <si>
-    <t>CCGT_7</t>
-  </si>
-  <si>
-    <t>CCGT_8</t>
-  </si>
-  <si>
-    <t>CCGT_9</t>
-  </si>
-  <si>
-    <t>OCGT_1</t>
-  </si>
-  <si>
-    <t>OCGT_2</t>
-  </si>
-  <si>
-    <t>OCGT_3</t>
-  </si>
-  <si>
-    <t>OCGT_4</t>
-  </si>
-  <si>
-    <t>OCGT_5</t>
-  </si>
-  <si>
-    <t>FuelOilGas</t>
-  </si>
-  <si>
-    <t>Node_9</t>
+    <t>StylizedAustriaInEurope</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>NOETKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_NOE</t>
+  </si>
+  <si>
+    <t>WIETKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_WIE</t>
+  </si>
+  <si>
+    <t>STMKTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_STMK</t>
+  </si>
+  <si>
+    <t>OOETKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_OOE</t>
+  </si>
+  <si>
+    <t>SBGTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_SBG</t>
+  </si>
+  <si>
+    <t>ALTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_AL</t>
+  </si>
+  <si>
+    <t>BETKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_BE</t>
+  </si>
+  <si>
+    <t>BGTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_BG</t>
+  </si>
+  <si>
+    <t>CZTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_CZ</t>
+  </si>
+  <si>
+    <t>DETKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_DE</t>
+  </si>
+  <si>
+    <t>ESTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_ES</t>
+  </si>
+  <si>
+    <t>FRTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_FR</t>
+  </si>
+  <si>
+    <t>GRTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_EL</t>
+  </si>
+  <si>
+    <t>HRTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_HR</t>
+  </si>
+  <si>
+    <t>HUTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_HU</t>
+  </si>
+  <si>
+    <t>ITTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_IT</t>
+  </si>
+  <si>
+    <t>NLTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_NL</t>
+  </si>
+  <si>
+    <t>PLTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_PL</t>
+  </si>
+  <si>
+    <t>PTTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_PT</t>
+  </si>
+  <si>
+    <t>ROTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_RO</t>
+  </si>
+  <si>
+    <t>RSTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_RS</t>
+  </si>
+  <si>
+    <t>SITKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_SI</t>
+  </si>
+  <si>
+    <t>SKTKWCNG</t>
+  </si>
+  <si>
+    <t>Nod_SK</t>
+  </si>
+  <si>
+    <t>ALTKWCOG</t>
+  </si>
+  <si>
+    <t>BETKWCOG</t>
+  </si>
+  <si>
+    <t>CZTKWCOG</t>
+  </si>
+  <si>
+    <t>DETKWCOG</t>
+  </si>
+  <si>
+    <t>DKTKWCOG</t>
+  </si>
+  <si>
+    <t>Nod_DK</t>
+  </si>
+  <si>
+    <t>DWTKWCOG</t>
+  </si>
+  <si>
+    <t>Nod_DW</t>
+  </si>
+  <si>
+    <t>GRTKWCOG</t>
+  </si>
+  <si>
+    <t>HUTKWCOG</t>
+  </si>
+  <si>
+    <t>ITTKWCOG</t>
+  </si>
+  <si>
+    <t>NLTKWCOG</t>
+  </si>
+  <si>
+    <t>SKTKWCOG</t>
+  </si>
+  <si>
+    <t>BETKWOOG</t>
+  </si>
+  <si>
+    <t>BGTKWOOG</t>
+  </si>
+  <si>
+    <t>DETKWOOG</t>
+  </si>
+  <si>
+    <t>DKTKWOOG</t>
+  </si>
+  <si>
+    <t>DWTKWOOG</t>
+  </si>
+  <si>
+    <t>FRTKWOOG</t>
+  </si>
+  <si>
+    <t>GRTKWOOG</t>
+  </si>
+  <si>
+    <t>HUTKWOOG</t>
+  </si>
+  <si>
+    <t>ITTKWOOG</t>
+  </si>
+  <si>
+    <t>NLTKWOOG</t>
+  </si>
+  <si>
+    <t>ROTKWOOG</t>
+  </si>
+  <si>
+    <t>RSTKWOOG</t>
+  </si>
+  <si>
+    <t>SITKWOOG</t>
+  </si>
+  <si>
+    <t>SKTKWOOG</t>
+  </si>
+  <si>
+    <t>BETKWONG</t>
+  </si>
+  <si>
+    <t>BGTKWONG</t>
+  </si>
+  <si>
+    <t>DETKWONG</t>
+  </si>
+  <si>
+    <t>DKTKWONG</t>
+  </si>
+  <si>
+    <t>DWTKWONG</t>
+  </si>
+  <si>
+    <t>FRTKWONG</t>
+  </si>
+  <si>
+    <t>ITTKWONG</t>
+  </si>
+  <si>
+    <t>NLTKWONG</t>
+  </si>
+  <si>
+    <t>PLTKWONG</t>
+  </si>
+  <si>
+    <t>ROTKWONG</t>
+  </si>
+  <si>
+    <t>BETKWO</t>
+  </si>
+  <si>
+    <t>Oil</t>
+  </si>
+  <si>
+    <t>BGTKWO</t>
+  </si>
+  <si>
+    <t>CHTKWO</t>
+  </si>
+  <si>
+    <t>Nod_CH</t>
+  </si>
+  <si>
+    <t>CZTKWO</t>
+  </si>
+  <si>
+    <t>DKTKWO</t>
+  </si>
+  <si>
+    <t>DWTKWO</t>
+  </si>
+  <si>
+    <t>ESTKWO</t>
+  </si>
+  <si>
+    <t>FRTKWO</t>
+  </si>
+  <si>
+    <t>HUTKWO</t>
+  </si>
+  <si>
+    <t>ITTKWO</t>
+  </si>
+  <si>
+    <t>LUTKWO</t>
+  </si>
+  <si>
+    <t>Nod_LU</t>
+  </si>
+  <si>
+    <t>NLTKWO</t>
+  </si>
+  <si>
+    <t>PLTKWO</t>
+  </si>
+  <si>
+    <t>ROTKWO</t>
+  </si>
+  <si>
+    <t>SKTKWO</t>
+  </si>
+  <si>
+    <t>CZTKWN</t>
+  </si>
+  <si>
+    <t>FRTKWN</t>
+  </si>
+  <si>
+    <t>ROTKWN</t>
+  </si>
+  <si>
+    <t>SITKWN</t>
+  </si>
+  <si>
+    <t>SKTKWN</t>
+  </si>
+  <si>
+    <t>BETKWB</t>
+  </si>
+  <si>
+    <t>Biomass</t>
+  </si>
+  <si>
+    <t>DKTKWB</t>
+  </si>
+  <si>
+    <t>DWTKWB</t>
+  </si>
+  <si>
+    <t>SKTKWB</t>
   </si>
 </sst>
 </file>
@@ -958,7 +1217,7 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:AE27"/>
+  <dimension ref="A1:AE89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.5703125" customWidth="1"/>
@@ -1492,28 +1751,28 @@
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F8" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="14">
-        <v>771.6</v>
+        <v>133</v>
       </c>
       <c r="H8" s="14">
-        <v>771.6</v>
+        <v>0</v>
       </c>
       <c r="I8" s="14">
-        <v>0</v>
+        <v>33.25</v>
       </c>
       <c r="J8" s="14">
-        <v>0</v>
+        <v>33.25</v>
       </c>
       <c r="K8" s="13">
         <v>1</v>
@@ -1522,30 +1781,32 @@
         <v>1</v>
       </c>
       <c r="M8" s="14">
-        <v>0</v>
+        <v>66.5</v>
       </c>
       <c r="N8" s="14">
-        <v>0</v>
+        <v>-66.5</v>
       </c>
       <c r="O8" s="14">
         <v>8</v>
       </c>
       <c r="P8" s="15">
-        <v>860</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q8" s="15">
-        <v>57.333333333333343</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R8" s="15">
-        <v>0</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S8" s="15">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8" s="15">
-        <v>0</v>
-      </c>
-      <c r="U8" s="15"/>
+        <v>0.17324561111111017</v>
+      </c>
+      <c r="U8" s="15">
+        <v>0</v>
+      </c>
       <c r="V8" s="13">
         <v>0</v>
       </c>
@@ -1556,20 +1817,12 @@
         <v>0.97</v>
       </c>
       <c r="Y8" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA8" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB8" s="18">
-        <v>47.491300000000003</v>
-      </c>
-      <c r="AC8" s="18">
-        <v>12.818199999999999</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z8" s="13"/>
+      <c r="AA8" s="13"/>
+      <c r="AB8" s="18"/>
+      <c r="AC8" s="18"/>
       <c r="AD8" s="19" t="s">
         <v>97</v>
       </c>
@@ -1581,28 +1834,28 @@
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="13">
         <v>1</v>
       </c>
       <c r="G9" s="14">
-        <v>588</v>
+        <v>576</v>
       </c>
       <c r="H9" s="14">
-        <v>235.2</v>
+        <v>0</v>
       </c>
       <c r="I9" s="14">
-        <v>88.2</v>
+        <v>144</v>
       </c>
       <c r="J9" s="14">
-        <v>88.2</v>
+        <v>144</v>
       </c>
       <c r="K9" s="13">
         <v>1</v>
@@ -1611,54 +1864,48 @@
         <v>1</v>
       </c>
       <c r="M9" s="14">
-        <v>176.4</v>
+        <v>288</v>
       </c>
       <c r="N9" s="14">
-        <v>-176.4</v>
+        <v>-288</v>
       </c>
       <c r="O9" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P9" s="15">
-        <v>17.2</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q9" s="15">
-        <v>0.35833333333333328</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R9" s="15">
-        <v>58.139534883720927</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S9" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T9" s="15">
-        <v>2325.5813953488368</v>
-      </c>
-      <c r="U9" s="15"/>
+        <v>0.17324561111111017</v>
+      </c>
+      <c r="U9" s="15">
+        <v>0</v>
+      </c>
       <c r="V9" s="13">
         <v>0</v>
       </c>
       <c r="W9" s="15">
-        <v>145591.30710000001</v>
+        <v>0</v>
       </c>
       <c r="X9" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Y9" s="17">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="Z9" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA9" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB9" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC9" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="18"/>
+      <c r="AC9" s="18"/>
       <c r="AD9" s="19" t="s">
         <v>97</v>
       </c>
@@ -1670,28 +1917,28 @@
       <c r="A10" s="10"/>
       <c r="B10" s="11"/>
       <c r="C10" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F10" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="14">
-        <v>203.1</v>
+        <v>222</v>
       </c>
       <c r="H10" s="14">
-        <v>81.239999999999995</v>
+        <v>0</v>
       </c>
       <c r="I10" s="14">
-        <v>30.465</v>
+        <v>55.5</v>
       </c>
       <c r="J10" s="14">
-        <v>30.465</v>
+        <v>55.5</v>
       </c>
       <c r="K10" s="13">
         <v>1</v>
@@ -1700,54 +1947,48 @@
         <v>1</v>
       </c>
       <c r="M10" s="14">
-        <v>60.93</v>
+        <v>111</v>
       </c>
       <c r="N10" s="14">
-        <v>-60.93</v>
+        <v>-111</v>
       </c>
       <c r="O10" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P10" s="15">
-        <v>17.63</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q10" s="15">
-        <v>0.37391304347826088</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R10" s="15">
-        <v>58.139534883720927</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S10" s="15">
-        <v>6.05</v>
+        <v>4</v>
       </c>
       <c r="T10" s="15">
-        <v>2325.5813953488368</v>
-      </c>
-      <c r="U10" s="15"/>
+        <v>0.17324561111111017</v>
+      </c>
+      <c r="U10" s="15">
+        <v>0</v>
+      </c>
       <c r="V10" s="13">
         <v>0</v>
       </c>
       <c r="W10" s="15">
-        <v>146591.30710000001</v>
+        <v>0</v>
       </c>
       <c r="X10" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Y10" s="17">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="Z10" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA10" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB10" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC10" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="18"/>
+      <c r="AC10" s="18"/>
       <c r="AD10" s="19" t="s">
         <v>97</v>
       </c>
@@ -1759,28 +2000,28 @@
       <c r="A11" s="10"/>
       <c r="B11" s="11"/>
       <c r="C11" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F11" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="14">
-        <v>150.4</v>
+        <v>238</v>
       </c>
       <c r="H11" s="14">
-        <v>60.16</v>
+        <v>0</v>
       </c>
       <c r="I11" s="14">
-        <v>22.56</v>
+        <v>59.5</v>
       </c>
       <c r="J11" s="14">
-        <v>22.56</v>
+        <v>59.5</v>
       </c>
       <c r="K11" s="13">
         <v>1</v>
@@ -1789,54 +2030,48 @@
         <v>1</v>
       </c>
       <c r="M11" s="14">
-        <v>45.12</v>
+        <v>119</v>
       </c>
       <c r="N11" s="14">
-        <v>-45.12</v>
+        <v>-119</v>
       </c>
       <c r="O11" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P11" s="15">
-        <v>18.059999999999999</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q11" s="15">
-        <v>0.37391304347826088</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R11" s="15">
-        <v>58.139534883720927</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S11" s="15">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="T11" s="15">
-        <v>2325.5813953488368</v>
-      </c>
-      <c r="U11" s="15"/>
+        <v>0.17324561111111017</v>
+      </c>
+      <c r="U11" s="15">
+        <v>0</v>
+      </c>
       <c r="V11" s="13">
         <v>0</v>
       </c>
       <c r="W11" s="15">
-        <v>147591.30710000001</v>
+        <v>0</v>
       </c>
       <c r="X11" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Y11" s="17">
-        <v>0.33200000000000002</v>
-      </c>
-      <c r="Z11" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA11" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB11" s="18">
-        <v>46.561055000000003</v>
-      </c>
-      <c r="AC11" s="18">
-        <v>14.479570000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="18"/>
+      <c r="AC11" s="18"/>
       <c r="AD11" s="19" t="s">
         <v>97</v>
       </c>
@@ -1848,28 +2083,28 @@
       <c r="A12" s="10"/>
       <c r="B12" s="11"/>
       <c r="C12" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F12" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="14">
-        <v>194.4</v>
+        <v>7</v>
       </c>
       <c r="H12" s="14">
-        <v>77.760000000000005</v>
+        <v>0</v>
       </c>
       <c r="I12" s="14">
-        <v>29.16</v>
+        <v>1.75</v>
       </c>
       <c r="J12" s="14">
-        <v>29.16</v>
+        <v>1.75</v>
       </c>
       <c r="K12" s="13">
         <v>1</v>
@@ -1878,54 +2113,48 @@
         <v>1</v>
       </c>
       <c r="M12" s="14">
-        <v>58.32</v>
+        <v>3.5</v>
       </c>
       <c r="N12" s="14">
-        <v>-58.32</v>
+        <v>-3.5</v>
       </c>
       <c r="O12" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P12" s="15">
-        <v>18.489999999999998</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q12" s="15">
-        <v>0.39090909090909087</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R12" s="15">
-        <v>58.139534883720927</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S12" s="15">
-        <v>6.15</v>
+        <v>4</v>
       </c>
       <c r="T12" s="15">
-        <v>2325.5813953488368</v>
-      </c>
-      <c r="U12" s="15"/>
+        <v>0.17324561111111017</v>
+      </c>
+      <c r="U12" s="15">
+        <v>0</v>
+      </c>
       <c r="V12" s="13">
         <v>0</v>
       </c>
       <c r="W12" s="15">
-        <v>148591.30710000001</v>
+        <v>0</v>
       </c>
       <c r="X12" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Y12" s="17">
-        <v>0.31900000000000001</v>
-      </c>
-      <c r="Z12" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB12" s="18">
-        <v>47.055199999999999</v>
-      </c>
-      <c r="AC12" s="18">
-        <v>9.9000199999999996</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="18"/>
       <c r="AD12" s="19" t="s">
         <v>97</v>
       </c>
@@ -1937,84 +2166,78 @@
       <c r="A13" s="10"/>
       <c r="B13" s="11"/>
       <c r="C13" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>110</v>
       </c>
       <c r="F13" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" s="14">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="H13" s="14">
+        <v>0</v>
+      </c>
+      <c r="I13" s="14">
+        <v>50</v>
+      </c>
+      <c r="J13" s="14">
+        <v>50</v>
+      </c>
+      <c r="K13" s="13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="13">
+        <v>1</v>
+      </c>
+      <c r="M13" s="14">
         <v>100</v>
       </c>
-      <c r="I13" s="14">
-        <v>200</v>
-      </c>
-      <c r="J13" s="14">
-        <v>200</v>
-      </c>
-      <c r="K13" s="13">
-        <v>1</v>
-      </c>
-      <c r="L13" s="13">
-        <v>1</v>
-      </c>
-      <c r="M13" s="14">
-        <v>200</v>
-      </c>
       <c r="N13" s="14">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O13" s="14">
+        <v>8</v>
+      </c>
+      <c r="P13" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q13" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R13" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S13" s="15">
         <v>4</v>
       </c>
-      <c r="P13" s="15">
-        <v>25.8</v>
-      </c>
-      <c r="Q13" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R13" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S13" s="15">
-        <v>3.8</v>
-      </c>
       <c r="T13" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U13" s="15"/>
+        <v>2038.1836601307077</v>
+      </c>
+      <c r="U13" s="15">
+        <v>0</v>
+      </c>
       <c r="V13" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W13" s="15">
-        <v>41818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X13" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y13" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z13" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA13" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB13" s="18">
-        <v>47.066462000000001</v>
-      </c>
-      <c r="AC13" s="18">
-        <v>9.9157949999999992</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="18"/>
+      <c r="AC13" s="18"/>
       <c r="AD13" s="19" t="s">
         <v>97</v>
       </c>
@@ -2029,25 +2252,25 @@
         <v>111</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F14" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="14">
-        <v>500</v>
+        <v>6164.3000002999997</v>
       </c>
       <c r="H14" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I14" s="14">
-        <v>100</v>
+        <v>1541.075</v>
       </c>
       <c r="J14" s="14">
-        <v>100</v>
+        <v>1541.075</v>
       </c>
       <c r="K14" s="13">
         <v>1</v>
@@ -2056,54 +2279,48 @@
         <v>1</v>
       </c>
       <c r="M14" s="14">
-        <v>200</v>
+        <v>3082.15</v>
       </c>
       <c r="N14" s="14">
-        <v>-200</v>
+        <v>-3082.15</v>
       </c>
       <c r="O14" s="14">
+        <v>8</v>
+      </c>
+      <c r="P14" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q14" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R14" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S14" s="15">
         <v>4</v>
       </c>
-      <c r="P14" s="15">
-        <v>27.52</v>
-      </c>
-      <c r="Q14" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R14" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S14" s="15">
-        <v>3.85</v>
-      </c>
       <c r="T14" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U14" s="15"/>
+        <v>62819.877683775871</v>
+      </c>
+      <c r="U14" s="15">
+        <v>0</v>
+      </c>
       <c r="V14" s="13">
         <v>0</v>
       </c>
       <c r="W14" s="15">
-        <v>42818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X14" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y14" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z14" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB14" s="18">
-        <v>47.491300000000003</v>
-      </c>
-      <c r="AC14" s="18">
-        <v>12.818199999999999</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="18"/>
+      <c r="AC14" s="18"/>
       <c r="AD14" s="19" t="s">
         <v>97</v>
       </c>
@@ -2115,28 +2332,28 @@
       <c r="A15" s="10"/>
       <c r="B15" s="11"/>
       <c r="C15" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F15" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>500</v>
+        <v>752</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="J15" s="14">
-        <v>100</v>
+        <v>188</v>
       </c>
       <c r="K15" s="13">
         <v>1</v>
@@ -2145,87 +2362,81 @@
         <v>1</v>
       </c>
       <c r="M15" s="14">
-        <v>200</v>
+        <v>376</v>
       </c>
       <c r="N15" s="14">
-        <v>-200</v>
+        <v>-376</v>
       </c>
       <c r="O15" s="14">
+        <v>8</v>
+      </c>
+      <c r="P15" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q15" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R15" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S15" s="15">
         <v>4</v>
       </c>
-      <c r="P15" s="15">
-        <v>29.24</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R15" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S15" s="15">
-        <v>3.9</v>
-      </c>
       <c r="T15" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U15" s="15"/>
+        <v>7663.5705620914605</v>
+      </c>
+      <c r="U15" s="15">
+        <v>0</v>
+      </c>
       <c r="V15" s="13">
         <v>0</v>
       </c>
       <c r="W15" s="15">
-        <v>43818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X15" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y15" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z15" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB15" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC15" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="18"/>
+      <c r="AC15" s="18"/>
       <c r="AD15" s="19" t="s">
         <v>97</v>
       </c>
       <c r="AE15" s="19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A16" s="10"/>
       <c r="B16" s="11"/>
       <c r="C16" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="F16" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" s="14">
-        <v>500</v>
+        <v>3205</v>
       </c>
       <c r="H16" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>100</v>
+        <v>801.25</v>
       </c>
       <c r="J16" s="14">
-        <v>100</v>
+        <v>801.25</v>
       </c>
       <c r="K16" s="13">
         <v>1</v>
@@ -2234,89 +2445,81 @@
         <v>1</v>
       </c>
       <c r="M16" s="14">
-        <v>200</v>
+        <v>1602.5</v>
       </c>
       <c r="N16" s="14">
-        <v>-200</v>
+        <v>-1602.5</v>
       </c>
       <c r="O16" s="14">
+        <v>8</v>
+      </c>
+      <c r="P16" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R16" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S16" s="15">
         <v>4</v>
       </c>
-      <c r="P16" s="15">
-        <v>30.96</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R16" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S16" s="15">
-        <v>3.95</v>
-      </c>
       <c r="T16" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U16" s="15"/>
+        <v>32661.893153594589</v>
+      </c>
+      <c r="U16" s="15">
+        <v>0</v>
+      </c>
       <c r="V16" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" s="15">
-        <v>44818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X16" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y16" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z16" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB16" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC16" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="18"/>
+      <c r="AC16" s="18"/>
       <c r="AD16" s="19" t="s">
         <v>97</v>
       </c>
       <c r="AE16" s="19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>115</v>
-      </c>
+      <c r="A17" s="10"/>
       <c r="B17" s="11"/>
       <c r="C17" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="14">
-        <v>500</v>
+        <v>23332</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>100</v>
+        <v>5833</v>
       </c>
       <c r="J17" s="14">
-        <v>100</v>
+        <v>5833</v>
       </c>
       <c r="K17" s="13">
         <v>1</v>
@@ -2325,54 +2528,48 @@
         <v>1</v>
       </c>
       <c r="M17" s="14">
-        <v>200</v>
+        <v>11666</v>
       </c>
       <c r="N17" s="14">
-        <v>-200</v>
+        <v>-11666</v>
       </c>
       <c r="O17" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" s="15">
-        <v>32.68</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q17" s="15">
-        <v>0.4777777777777778</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R17" s="15">
-        <v>348.83720930232562</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S17" s="15">
         <v>4</v>
       </c>
       <c r="T17" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U17" s="15"/>
+        <v>237774.50579084834</v>
+      </c>
+      <c r="U17" s="15">
+        <v>0</v>
+      </c>
       <c r="V17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W17" s="15">
-        <v>45818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X17" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y17" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB17" s="18">
-        <v>46.561055000000003</v>
-      </c>
-      <c r="AC17" s="18">
-        <v>14.479570000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="18"/>
+      <c r="AC17" s="18"/>
       <c r="AD17" s="19" t="s">
         <v>97</v>
       </c>
@@ -2384,28 +2581,28 @@
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="F18" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14">
-        <v>500</v>
+        <v>24498.560000000001</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>100</v>
+        <v>6124.64</v>
       </c>
       <c r="J18" s="14">
-        <v>100</v>
+        <v>6124.64</v>
       </c>
       <c r="K18" s="13">
         <v>1</v>
@@ -2414,54 +2611,48 @@
         <v>1</v>
       </c>
       <c r="M18" s="14">
-        <v>200</v>
+        <v>12249.28</v>
       </c>
       <c r="N18" s="14">
-        <v>-200</v>
+        <v>-12249.28</v>
       </c>
       <c r="O18" s="14">
+        <v>8</v>
+      </c>
+      <c r="P18" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q18" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R18" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S18" s="15">
         <v>4</v>
       </c>
-      <c r="P18" s="15">
-        <v>34.4</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R18" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S18" s="15">
-        <v>4.05</v>
-      </c>
       <c r="T18" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U18" s="15"/>
+        <v>249662.82344365877</v>
+      </c>
+      <c r="U18" s="15">
+        <v>0</v>
+      </c>
       <c r="V18" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="15">
-        <v>46818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X18" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y18" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z18" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB18" s="18">
-        <v>47.055199999999999</v>
-      </c>
-      <c r="AC18" s="18">
-        <v>9.9000199999999996</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="18"/>
+      <c r="AC18" s="18"/>
       <c r="AD18" s="19" t="s">
         <v>97</v>
       </c>
@@ -2473,28 +2664,28 @@
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="F19" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="14">
-        <v>500</v>
+        <v>6552.9999995999997</v>
       </c>
       <c r="H19" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>100</v>
+        <v>1638.25</v>
       </c>
       <c r="J19" s="14">
-        <v>100</v>
+        <v>1638.25</v>
       </c>
       <c r="K19" s="13">
         <v>1</v>
@@ -2503,54 +2694,48 @@
         <v>1</v>
       </c>
       <c r="M19" s="14">
-        <v>200</v>
+        <v>3276.5</v>
       </c>
       <c r="N19" s="14">
-        <v>-200</v>
+        <v>-3276.5</v>
       </c>
       <c r="O19" s="14">
+        <v>8</v>
+      </c>
+      <c r="P19" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R19" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S19" s="15">
         <v>4</v>
       </c>
-      <c r="P19" s="15">
-        <v>36.119999999999997</v>
-      </c>
-      <c r="Q19" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R19" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S19" s="15">
-        <v>4.0999999999999996</v>
-      </c>
       <c r="T19" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U19" s="15"/>
+        <v>66781.087620106264</v>
+      </c>
+      <c r="U19" s="15">
+        <v>0</v>
+      </c>
       <c r="V19" s="13">
         <v>0</v>
       </c>
       <c r="W19" s="15">
-        <v>47818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X19" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y19" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z19" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB19" s="18">
-        <v>47.066462000000001</v>
-      </c>
-      <c r="AC19" s="18">
-        <v>9.9157949999999992</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="18"/>
+      <c r="AC19" s="18"/>
       <c r="AD19" s="19" t="s">
         <v>97</v>
       </c>
@@ -2562,28 +2747,28 @@
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
       <c r="C20" s="12" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="F20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="14">
-        <v>500</v>
+        <v>6347.1000002000001</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>100</v>
+        <v>1586.7750000000001</v>
       </c>
       <c r="J20" s="14">
-        <v>100</v>
+        <v>1586.7750000000001</v>
       </c>
       <c r="K20" s="13">
         <v>1</v>
@@ -2592,54 +2777,48 @@
         <v>1</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>3173.55</v>
       </c>
       <c r="N20" s="14">
-        <v>-200</v>
+        <v>-3173.55</v>
       </c>
       <c r="O20" s="14">
+        <v>8</v>
+      </c>
+      <c r="P20" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q20" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R20" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S20" s="15">
         <v>4</v>
       </c>
-      <c r="P20" s="15">
-        <v>37.840000000000003</v>
-      </c>
-      <c r="Q20" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R20" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S20" s="15">
-        <v>4.1500000000000004</v>
-      </c>
       <c r="T20" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U20" s="15"/>
+        <v>64682.777548116253</v>
+      </c>
+      <c r="U20" s="15">
+        <v>0</v>
+      </c>
       <c r="V20" s="13">
         <v>0</v>
       </c>
       <c r="W20" s="15">
-        <v>48818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X20" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y20" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z20" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB20" s="18">
-        <v>47.491300000000003</v>
-      </c>
-      <c r="AC20" s="18">
-        <v>12.818199999999999</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="18"/>
+      <c r="AC20" s="18"/>
       <c r="AD20" s="19" t="s">
         <v>97</v>
       </c>
@@ -2651,28 +2830,28 @@
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="F21" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="14">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="H21" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I21" s="14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J21" s="14">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K21" s="13">
         <v>1</v>
@@ -2681,54 +2860,48 @@
         <v>1</v>
       </c>
       <c r="M21" s="14">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="N21" s="14">
-        <v>-200</v>
+        <v>-190</v>
       </c>
       <c r="O21" s="14">
+        <v>8</v>
+      </c>
+      <c r="P21" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q21" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R21" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S21" s="15">
         <v>4</v>
       </c>
-      <c r="P21" s="15">
-        <v>39.56</v>
-      </c>
-      <c r="Q21" s="15">
-        <v>0.4777777777777778</v>
-      </c>
-      <c r="R21" s="15">
-        <v>348.83720930232562</v>
-      </c>
-      <c r="S21" s="15">
-        <v>4.2</v>
-      </c>
       <c r="T21" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U21" s="15"/>
+        <v>3872.5489542483447</v>
+      </c>
+      <c r="U21" s="15">
+        <v>0</v>
+      </c>
       <c r="V21" s="13">
         <v>0</v>
       </c>
       <c r="W21" s="15">
-        <v>49818.779699999999</v>
+        <v>0</v>
       </c>
       <c r="X21" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y21" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z21" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA21" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB21" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC21" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="18"/>
+      <c r="AC21" s="18"/>
       <c r="AD21" s="19" t="s">
         <v>97</v>
       </c>
@@ -2740,28 +2913,28 @@
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="F22" s="13">
         <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>400</v>
+        <v>1344</v>
       </c>
       <c r="H22" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="J22" s="14">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="K22" s="13">
         <v>1</v>
@@ -2770,54 +2943,48 @@
         <v>1</v>
       </c>
       <c r="M22" s="14">
-        <v>180</v>
+        <v>672</v>
       </c>
       <c r="N22" s="14">
-        <v>-180</v>
+        <v>-672</v>
       </c>
       <c r="O22" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P22" s="15">
-        <v>26.058</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q22" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R22" s="15">
-        <v>116.2790697674419</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S22" s="15">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="T22" s="15">
-        <v>0</v>
-      </c>
-      <c r="U22" s="15"/>
+        <v>13696.594196078355</v>
+      </c>
+      <c r="U22" s="15">
+        <v>0</v>
+      </c>
       <c r="V22" s="13">
         <v>0</v>
       </c>
       <c r="W22" s="15">
-        <v>24781.499100000001</v>
+        <v>0</v>
       </c>
       <c r="X22" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y22" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z22" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA22" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB22" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC22" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="18"/>
+      <c r="AC22" s="18"/>
       <c r="AD22" s="19" t="s">
         <v>97</v>
       </c>
@@ -2829,28 +2996,28 @@
       <c r="A23" s="10"/>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="F23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="14">
-        <v>400</v>
+        <v>33812.799999199997</v>
       </c>
       <c r="H23" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>360</v>
+        <v>8453.2000000000007</v>
       </c>
       <c r="J23" s="14">
-        <v>360</v>
+        <v>8453.2000000000007</v>
       </c>
       <c r="K23" s="13">
         <v>1</v>
@@ -2859,54 +3026,48 @@
         <v>1</v>
       </c>
       <c r="M23" s="14">
-        <v>180</v>
+        <v>16906.400000000001</v>
       </c>
       <c r="N23" s="14">
-        <v>-180</v>
+        <v>-16906.400000000001</v>
       </c>
       <c r="O23" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P23" s="15">
-        <v>26.315999999999999</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q23" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R23" s="15">
-        <v>116.2790697674419</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S23" s="15">
-        <v>4.0599999999999996</v>
+        <v>4</v>
       </c>
       <c r="T23" s="15">
-        <v>0</v>
-      </c>
-      <c r="U23" s="15"/>
+        <v>344583.48230818514</v>
+      </c>
+      <c r="U23" s="15">
+        <v>0</v>
+      </c>
       <c r="V23" s="13">
         <v>0</v>
       </c>
       <c r="W23" s="15">
-        <v>25781.499100000001</v>
+        <v>0</v>
       </c>
       <c r="X23" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y23" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z23" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA23" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB23" s="18">
-        <v>46.561055000000003</v>
-      </c>
-      <c r="AC23" s="18">
-        <v>14.479570000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="18"/>
+      <c r="AC23" s="18"/>
       <c r="AD23" s="19" t="s">
         <v>97</v>
       </c>
@@ -2918,28 +3079,28 @@
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="F24" s="13">
         <v>1</v>
       </c>
       <c r="G24" s="14">
-        <v>400</v>
+        <v>17598</v>
       </c>
       <c r="H24" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>360</v>
+        <v>4399.5</v>
       </c>
       <c r="J24" s="14">
-        <v>360</v>
+        <v>4399.5</v>
       </c>
       <c r="K24" s="13">
         <v>1</v>
@@ -2948,54 +3109,48 @@
         <v>1</v>
       </c>
       <c r="M24" s="14">
-        <v>180</v>
+        <v>8799</v>
       </c>
       <c r="N24" s="14">
-        <v>-180</v>
+        <v>-8799</v>
       </c>
       <c r="O24" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P24" s="15">
-        <v>26.574000000000002</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q24" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R24" s="15">
-        <v>116.2790697674419</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S24" s="15">
-        <v>4.09</v>
+        <v>4</v>
       </c>
       <c r="T24" s="15">
-        <v>0</v>
-      </c>
-      <c r="U24" s="15"/>
+        <v>179339.78025490098</v>
+      </c>
+      <c r="U24" s="15">
+        <v>0</v>
+      </c>
       <c r="V24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W24" s="15">
-        <v>26781.499100000001</v>
+        <v>0</v>
       </c>
       <c r="X24" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y24" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z24" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA24" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB24" s="18">
-        <v>47.055199999999999</v>
-      </c>
-      <c r="AC24" s="18">
-        <v>9.9000199999999996</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="18"/>
+      <c r="AC24" s="18"/>
       <c r="AD24" s="19" t="s">
         <v>97</v>
       </c>
@@ -3007,28 +3162,28 @@
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="F25" s="13">
         <v>1</v>
       </c>
       <c r="G25" s="14">
-        <v>400</v>
+        <v>7689.3000001999999</v>
       </c>
       <c r="H25" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>360</v>
+        <v>1922.325</v>
       </c>
       <c r="J25" s="14">
-        <v>360</v>
+        <v>1922.325</v>
       </c>
       <c r="K25" s="13">
         <v>1</v>
@@ -3037,87 +3192,81 @@
         <v>1</v>
       </c>
       <c r="M25" s="14">
-        <v>180</v>
+        <v>3844.65</v>
       </c>
       <c r="N25" s="14">
-        <v>-180</v>
+        <v>-3844.65</v>
       </c>
       <c r="O25" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P25" s="15">
-        <v>26.832000000000001</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q25" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R25" s="15">
-        <v>116.2790697674419</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S25" s="15">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="T25" s="15">
-        <v>0</v>
-      </c>
-      <c r="U25" s="15"/>
+        <v>78361.028091253422</v>
+      </c>
+      <c r="U25" s="15">
+        <v>0</v>
+      </c>
       <c r="V25" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W25" s="15">
-        <v>27781.499100000001</v>
+        <v>0</v>
       </c>
       <c r="X25" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y25" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z25" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA25" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB25" s="18">
-        <v>47.066462000000001</v>
-      </c>
-      <c r="AC25" s="18">
-        <v>9.9157949999999992</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="18"/>
+      <c r="AC25" s="18"/>
       <c r="AD25" s="19" t="s">
         <v>97</v>
       </c>
       <c r="AE25" s="19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="F26" s="13">
         <v>1</v>
       </c>
       <c r="G26" s="14">
-        <v>400</v>
+        <v>2839.0000002000002</v>
       </c>
       <c r="H26" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>360</v>
+        <v>709.75</v>
       </c>
       <c r="J26" s="14">
-        <v>360</v>
+        <v>709.75</v>
       </c>
       <c r="K26" s="13">
         <v>1</v>
@@ -3126,87 +3275,81 @@
         <v>1</v>
       </c>
       <c r="M26" s="14">
-        <v>180</v>
+        <v>1419.5</v>
       </c>
       <c r="N26" s="14">
-        <v>-180</v>
+        <v>-1419.5</v>
       </c>
       <c r="O26" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P26" s="15">
-        <v>27.09</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q26" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R26" s="15">
-        <v>116.2790697674419</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S26" s="15">
-        <v>4.1500000000000004</v>
+        <v>4</v>
       </c>
       <c r="T26" s="15">
-        <v>0</v>
-      </c>
-      <c r="U26" s="15"/>
+        <v>28932.017057593581</v>
+      </c>
+      <c r="U26" s="15">
+        <v>0</v>
+      </c>
       <c r="V26" s="13">
         <v>0</v>
       </c>
       <c r="W26" s="15">
-        <v>28781.499100000001</v>
+        <v>0</v>
       </c>
       <c r="X26" s="16">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="Y26" s="17">
-        <v>0.18099999999999999</v>
-      </c>
-      <c r="Z26" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA26" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB26" s="18">
-        <v>47.491300000000003</v>
-      </c>
-      <c r="AC26" s="18">
-        <v>12.818199999999999</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="18"/>
+      <c r="AC26" s="18"/>
       <c r="AD26" s="19" t="s">
         <v>97</v>
       </c>
       <c r="AE26" s="19" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F27" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>441.8</v>
+        <v>4006.3999994999999</v>
       </c>
       <c r="H27" s="14">
-        <v>44.18</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
-        <v>397.62</v>
+        <v>1001.6</v>
       </c>
       <c r="J27" s="14">
-        <v>397.62</v>
+        <v>1001.6</v>
       </c>
       <c r="K27" s="13">
         <v>1</v>
@@ -3215,58 +3358,5198 @@
         <v>1</v>
       </c>
       <c r="M27" s="14">
-        <v>198.81</v>
+        <v>2003.2</v>
       </c>
       <c r="N27" s="14">
-        <v>-198.81</v>
+        <v>-2003.2</v>
       </c>
       <c r="O27" s="14">
-        <v>2.5</v>
+        <v>8</v>
       </c>
       <c r="P27" s="15">
-        <v>51.6</v>
+        <v>14.620861006259339</v>
       </c>
       <c r="Q27" s="15">
-        <v>0.43</v>
+        <v>0.58003415756705989</v>
       </c>
       <c r="R27" s="15">
-        <v>348.83720930232562</v>
+        <v>11.627222222222159</v>
       </c>
       <c r="S27" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T27" s="15">
-        <v>1162.7906976744191</v>
-      </c>
-      <c r="U27" s="15"/>
+        <v>40828.895074642875</v>
+      </c>
+      <c r="U27" s="15">
+        <v>0</v>
+      </c>
       <c r="V27" s="13">
         <v>0</v>
       </c>
       <c r="W27" s="15">
-        <v>43367.623399999997</v>
+        <v>0</v>
       </c>
       <c r="X27" s="16">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="Y27" s="17">
-        <v>0.254</v>
-      </c>
-      <c r="Z27" s="13">
-        <v>2010</v>
-      </c>
-      <c r="AA27" s="13">
-        <v>2050</v>
-      </c>
-      <c r="AB27" s="18">
-        <v>46.77</v>
-      </c>
-      <c r="AC27" s="18">
-        <v>13.746700000000001</v>
-      </c>
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="18"/>
+      <c r="AC27" s="18"/>
       <c r="AD27" s="19" t="s">
         <v>97</v>
       </c>
       <c r="AE27" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="10"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1</v>
+      </c>
+      <c r="G28" s="14">
+        <v>182.90000001000001</v>
+      </c>
+      <c r="H28" s="14">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
+        <v>45.725000000000001</v>
+      </c>
+      <c r="J28" s="14">
+        <v>45.725000000000001</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1</v>
+      </c>
+      <c r="L28" s="13">
+        <v>1</v>
+      </c>
+      <c r="M28" s="14">
+        <v>91.45</v>
+      </c>
+      <c r="N28" s="14">
+        <v>-91.45</v>
+      </c>
+      <c r="O28" s="14">
+        <v>8</v>
+      </c>
+      <c r="P28" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q28" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R28" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S28" s="15">
+        <v>4</v>
+      </c>
+      <c r="T28" s="15">
+        <v>1863.9189572914413</v>
+      </c>
+      <c r="U28" s="15">
+        <v>0</v>
+      </c>
+      <c r="V28" s="13">
+        <v>0</v>
+      </c>
+      <c r="W28" s="15">
+        <v>0</v>
+      </c>
+      <c r="X28" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y28" s="17">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="18"/>
+      <c r="AC28" s="18"/>
+      <c r="AD28" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE28" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="10"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="13">
+        <v>1</v>
+      </c>
+      <c r="G29" s="14">
+        <v>114</v>
+      </c>
+      <c r="H29" s="14">
+        <v>0</v>
+      </c>
+      <c r="I29" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="J29" s="14">
+        <v>28.5</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1</v>
+      </c>
+      <c r="L29" s="13">
+        <v>1</v>
+      </c>
+      <c r="M29" s="14">
+        <v>57</v>
+      </c>
+      <c r="N29" s="14">
+        <v>-57</v>
+      </c>
+      <c r="O29" s="14">
+        <v>8</v>
+      </c>
+      <c r="P29" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q29" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R29" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S29" s="15">
+        <v>4</v>
+      </c>
+      <c r="T29" s="15">
+        <v>1161.7646862745032</v>
+      </c>
+      <c r="U29" s="15">
+        <v>0</v>
+      </c>
+      <c r="V29" s="13">
+        <v>0</v>
+      </c>
+      <c r="W29" s="15">
+        <v>0</v>
+      </c>
+      <c r="X29" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y29" s="17">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="18"/>
+      <c r="AC29" s="18"/>
+      <c r="AD29" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE29" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D30" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F30" s="13">
+        <v>1</v>
+      </c>
+      <c r="G30" s="14">
+        <v>411.49</v>
+      </c>
+      <c r="H30" s="14">
+        <v>0</v>
+      </c>
+      <c r="I30" s="14">
+        <v>102.873</v>
+      </c>
+      <c r="J30" s="14">
+        <v>102.873</v>
+      </c>
+      <c r="K30" s="13">
+        <v>1</v>
+      </c>
+      <c r="L30" s="13">
+        <v>1</v>
+      </c>
+      <c r="M30" s="14">
+        <v>205.745</v>
+      </c>
+      <c r="N30" s="14">
+        <v>-205.745</v>
+      </c>
+      <c r="O30" s="14">
+        <v>8</v>
+      </c>
+      <c r="P30" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q30" s="15">
+        <v>0.58003415756705989</v>
+      </c>
+      <c r="R30" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S30" s="15">
+        <v>4</v>
+      </c>
+      <c r="T30" s="15">
+        <v>4193.4609715359247</v>
+      </c>
+      <c r="U30" s="15">
+        <v>0</v>
+      </c>
+      <c r="V30" s="13">
+        <v>0</v>
+      </c>
+      <c r="W30" s="15">
+        <v>0</v>
+      </c>
+      <c r="X30" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y30" s="17">
+        <v>0.35299999999999998</v>
+      </c>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="18"/>
+      <c r="AC30" s="18"/>
+      <c r="AD30" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE30" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="10"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="13">
+        <v>1</v>
+      </c>
+      <c r="G31" s="14">
+        <v>100</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>25</v>
+      </c>
+      <c r="J31" s="14">
+        <v>25</v>
+      </c>
+      <c r="K31" s="13">
+        <v>1</v>
+      </c>
+      <c r="L31" s="13">
+        <v>1</v>
+      </c>
+      <c r="M31" s="14">
+        <v>50</v>
+      </c>
+      <c r="N31" s="14">
+        <v>-50</v>
+      </c>
+      <c r="O31" s="14">
+        <v>8</v>
+      </c>
+      <c r="P31" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q31" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R31" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S31" s="15">
+        <v>4</v>
+      </c>
+      <c r="T31" s="15">
+        <v>1244.7967320261369</v>
+      </c>
+      <c r="U31" s="15">
+        <v>0</v>
+      </c>
+      <c r="V31" s="13">
+        <v>0</v>
+      </c>
+      <c r="W31" s="15">
+        <v>0</v>
+      </c>
+      <c r="X31" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y31" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="18"/>
+      <c r="AC31" s="18"/>
+      <c r="AD31" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE31" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="10"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F32" s="13">
+        <v>1</v>
+      </c>
+      <c r="G32" s="14">
+        <v>950.3</v>
+      </c>
+      <c r="H32" s="14">
+        <v>0</v>
+      </c>
+      <c r="I32" s="14">
+        <v>237.57499999999999</v>
+      </c>
+      <c r="J32" s="14">
+        <v>237.57499999999999</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1</v>
+      </c>
+      <c r="L32" s="13">
+        <v>1</v>
+      </c>
+      <c r="M32" s="14">
+        <v>475.15</v>
+      </c>
+      <c r="N32" s="14">
+        <v>-475.15</v>
+      </c>
+      <c r="O32" s="14">
+        <v>8</v>
+      </c>
+      <c r="P32" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q32" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R32" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S32" s="15">
+        <v>4</v>
+      </c>
+      <c r="T32" s="15">
+        <v>11829.303344444379</v>
+      </c>
+      <c r="U32" s="15">
+        <v>0</v>
+      </c>
+      <c r="V32" s="13">
+        <v>0</v>
+      </c>
+      <c r="W32" s="15">
+        <v>0</v>
+      </c>
+      <c r="X32" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y32" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="18"/>
+      <c r="AC32" s="18"/>
+      <c r="AD32" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE32" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="10"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="13">
+        <v>1</v>
+      </c>
+      <c r="G33" s="14">
+        <v>509.4</v>
+      </c>
+      <c r="H33" s="14">
+        <v>0</v>
+      </c>
+      <c r="I33" s="14">
+        <v>127.35</v>
+      </c>
+      <c r="J33" s="14">
+        <v>127.35</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1</v>
+      </c>
+      <c r="L33" s="13">
+        <v>1</v>
+      </c>
+      <c r="M33" s="14">
+        <v>254.7</v>
+      </c>
+      <c r="N33" s="14">
+        <v>-254.7</v>
+      </c>
+      <c r="O33" s="14">
+        <v>8</v>
+      </c>
+      <c r="P33" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q33" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R33" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S33" s="15">
+        <v>4</v>
+      </c>
+      <c r="T33" s="15">
+        <v>6340.9945529411416</v>
+      </c>
+      <c r="U33" s="15">
+        <v>0</v>
+      </c>
+      <c r="V33" s="13">
+        <v>0</v>
+      </c>
+      <c r="W33" s="15">
+        <v>0</v>
+      </c>
+      <c r="X33" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="18"/>
+      <c r="AC33" s="18"/>
+      <c r="AD33" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE33" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A34" s="10"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="13">
+        <v>1</v>
+      </c>
+      <c r="G34" s="14">
+        <v>8086.8590008000001</v>
+      </c>
+      <c r="H34" s="14">
+        <v>0</v>
+      </c>
+      <c r="I34" s="14">
+        <v>2021.7149999999999</v>
+      </c>
+      <c r="J34" s="14">
+        <v>2021.7149999999999</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1</v>
+      </c>
+      <c r="L34" s="13">
+        <v>1</v>
+      </c>
+      <c r="M34" s="14">
+        <v>4043.43</v>
+      </c>
+      <c r="N34" s="14">
+        <v>-4043.43</v>
+      </c>
+      <c r="O34" s="14">
+        <v>8</v>
+      </c>
+      <c r="P34" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q34" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R34" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S34" s="15">
+        <v>4</v>
+      </c>
+      <c r="T34" s="15">
+        <v>100664.9565655199</v>
+      </c>
+      <c r="U34" s="15">
+        <v>0</v>
+      </c>
+      <c r="V34" s="13">
+        <v>0</v>
+      </c>
+      <c r="W34" s="15">
+        <v>0</v>
+      </c>
+      <c r="X34" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y34" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="18"/>
+      <c r="AC34" s="18"/>
+      <c r="AD34" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE34" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A35" s="10"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F35" s="13">
+        <v>1</v>
+      </c>
+      <c r="G35" s="14">
+        <v>138.5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>0</v>
+      </c>
+      <c r="I35" s="14">
+        <v>34.625</v>
+      </c>
+      <c r="J35" s="14">
+        <v>34.625</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1</v>
+      </c>
+      <c r="L35" s="13">
+        <v>1</v>
+      </c>
+      <c r="M35" s="14">
+        <v>69.25</v>
+      </c>
+      <c r="N35" s="14">
+        <v>-69.25</v>
+      </c>
+      <c r="O35" s="14">
+        <v>8</v>
+      </c>
+      <c r="P35" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q35" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R35" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S35" s="15">
+        <v>4</v>
+      </c>
+      <c r="T35" s="15">
+        <v>1724.0434738561994</v>
+      </c>
+      <c r="U35" s="15">
+        <v>0</v>
+      </c>
+      <c r="V35" s="13">
+        <v>0</v>
+      </c>
+      <c r="W35" s="15">
+        <v>0</v>
+      </c>
+      <c r="X35" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y35" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="18"/>
+      <c r="AC35" s="18"/>
+      <c r="AD35" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE35" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A36" s="10"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F36" s="13">
+        <v>1</v>
+      </c>
+      <c r="G36" s="14">
+        <v>195.55</v>
+      </c>
+      <c r="H36" s="14">
+        <v>0</v>
+      </c>
+      <c r="I36" s="14">
+        <v>48.887999999999998</v>
+      </c>
+      <c r="J36" s="14">
+        <v>48.887999999999998</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1</v>
+      </c>
+      <c r="L36" s="13">
+        <v>1</v>
+      </c>
+      <c r="M36" s="14">
+        <v>97.775000000000006</v>
+      </c>
+      <c r="N36" s="14">
+        <v>-97.775000000000006</v>
+      </c>
+      <c r="O36" s="14">
+        <v>8</v>
+      </c>
+      <c r="P36" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q36" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R36" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S36" s="15">
+        <v>4</v>
+      </c>
+      <c r="T36" s="15">
+        <v>2434.2000094771106</v>
+      </c>
+      <c r="U36" s="15">
+        <v>0</v>
+      </c>
+      <c r="V36" s="13">
+        <v>0</v>
+      </c>
+      <c r="W36" s="15">
+        <v>0</v>
+      </c>
+      <c r="X36" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y36" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="18"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE36" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A37" s="10"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F37" s="13">
+        <v>1</v>
+      </c>
+      <c r="G37" s="14">
+        <v>476.3</v>
+      </c>
+      <c r="H37" s="14">
+        <v>0</v>
+      </c>
+      <c r="I37" s="14">
+        <v>119.075</v>
+      </c>
+      <c r="J37" s="14">
+        <v>119.075</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1</v>
+      </c>
+      <c r="L37" s="13">
+        <v>1</v>
+      </c>
+      <c r="M37" s="14">
+        <v>238.15</v>
+      </c>
+      <c r="N37" s="14">
+        <v>-238.15</v>
+      </c>
+      <c r="O37" s="14">
+        <v>8</v>
+      </c>
+      <c r="P37" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q37" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R37" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S37" s="15">
+        <v>4</v>
+      </c>
+      <c r="T37" s="15">
+        <v>5928.9668346404906</v>
+      </c>
+      <c r="U37" s="15">
+        <v>0</v>
+      </c>
+      <c r="V37" s="13">
+        <v>0</v>
+      </c>
+      <c r="W37" s="15">
+        <v>0</v>
+      </c>
+      <c r="X37" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y37" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="18"/>
+      <c r="AC37" s="18"/>
+      <c r="AD37" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE37" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A38" s="10"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="13">
+        <v>1</v>
+      </c>
+      <c r="G38" s="14">
+        <v>102</v>
+      </c>
+      <c r="H38" s="14">
+        <v>0</v>
+      </c>
+      <c r="I38" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="J38" s="14">
+        <v>25.5</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1</v>
+      </c>
+      <c r="L38" s="13">
+        <v>1</v>
+      </c>
+      <c r="M38" s="14">
+        <v>51</v>
+      </c>
+      <c r="N38" s="14">
+        <v>-51</v>
+      </c>
+      <c r="O38" s="14">
+        <v>8</v>
+      </c>
+      <c r="P38" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q38" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R38" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S38" s="15">
+        <v>4</v>
+      </c>
+      <c r="T38" s="15">
+        <v>1269.6926666666598</v>
+      </c>
+      <c r="U38" s="15">
+        <v>0</v>
+      </c>
+      <c r="V38" s="13">
+        <v>0</v>
+      </c>
+      <c r="W38" s="15">
+        <v>0</v>
+      </c>
+      <c r="X38" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y38" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z38" s="13"/>
+      <c r="AA38" s="13"/>
+      <c r="AB38" s="18"/>
+      <c r="AC38" s="18"/>
+      <c r="AD38" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE38" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A39" s="10"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F39" s="13">
+        <v>1</v>
+      </c>
+      <c r="G39" s="14">
+        <v>1600.9999998000001</v>
+      </c>
+      <c r="H39" s="14">
+        <v>0</v>
+      </c>
+      <c r="I39" s="14">
+        <v>400.25</v>
+      </c>
+      <c r="J39" s="14">
+        <v>400.25</v>
+      </c>
+      <c r="K39" s="13">
+        <v>1</v>
+      </c>
+      <c r="L39" s="13">
+        <v>1</v>
+      </c>
+      <c r="M39" s="14">
+        <v>800.5</v>
+      </c>
+      <c r="N39" s="14">
+        <v>-800.5</v>
+      </c>
+      <c r="O39" s="14">
+        <v>8</v>
+      </c>
+      <c r="P39" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q39" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R39" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S39" s="15">
+        <v>4</v>
+      </c>
+      <c r="T39" s="15">
+        <v>19929.195677248859</v>
+      </c>
+      <c r="U39" s="15">
+        <v>0</v>
+      </c>
+      <c r="V39" s="13">
+        <v>0</v>
+      </c>
+      <c r="W39" s="15">
+        <v>0</v>
+      </c>
+      <c r="X39" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y39" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z39" s="13"/>
+      <c r="AA39" s="13"/>
+      <c r="AB39" s="18"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE39" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A40" s="10"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F40" s="13">
+        <v>1</v>
+      </c>
+      <c r="G40" s="14">
+        <v>3983.4999994999998</v>
+      </c>
+      <c r="H40" s="14">
+        <v>0</v>
+      </c>
+      <c r="I40" s="14">
+        <v>995.875</v>
+      </c>
+      <c r="J40" s="14">
+        <v>995.875</v>
+      </c>
+      <c r="K40" s="13">
+        <v>1</v>
+      </c>
+      <c r="L40" s="13">
+        <v>1</v>
+      </c>
+      <c r="M40" s="14">
+        <v>1991.75</v>
+      </c>
+      <c r="N40" s="14">
+        <v>-1991.75</v>
+      </c>
+      <c r="O40" s="14">
+        <v>8</v>
+      </c>
+      <c r="P40" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q40" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R40" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S40" s="15">
+        <v>4</v>
+      </c>
+      <c r="T40" s="15">
+        <v>49586.477814037178</v>
+      </c>
+      <c r="U40" s="15">
+        <v>0</v>
+      </c>
+      <c r="V40" s="13">
+        <v>0</v>
+      </c>
+      <c r="W40" s="15">
+        <v>0</v>
+      </c>
+      <c r="X40" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y40" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z40" s="13"/>
+      <c r="AA40" s="13"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE40" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A41" s="10"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F41" s="13">
+        <v>1</v>
+      </c>
+      <c r="G41" s="14">
+        <v>213.64999999999989</v>
+      </c>
+      <c r="H41" s="14">
+        <v>0</v>
+      </c>
+      <c r="I41" s="14">
+        <v>53.412999999999997</v>
+      </c>
+      <c r="J41" s="14">
+        <v>53.412999999999997</v>
+      </c>
+      <c r="K41" s="13">
+        <v>1</v>
+      </c>
+      <c r="L41" s="13">
+        <v>1</v>
+      </c>
+      <c r="M41" s="14">
+        <v>106.825</v>
+      </c>
+      <c r="N41" s="14">
+        <v>-106.825</v>
+      </c>
+      <c r="O41" s="14">
+        <v>8</v>
+      </c>
+      <c r="P41" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q41" s="15">
+        <v>0.46302726716129089</v>
+      </c>
+      <c r="R41" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S41" s="15">
+        <v>4</v>
+      </c>
+      <c r="T41" s="15">
+        <v>2659.5082179738401</v>
+      </c>
+      <c r="U41" s="15">
+        <v>0</v>
+      </c>
+      <c r="V41" s="13">
+        <v>0</v>
+      </c>
+      <c r="W41" s="15">
+        <v>0</v>
+      </c>
+      <c r="X41" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y41" s="17">
+        <v>0.47</v>
+      </c>
+      <c r="Z41" s="13"/>
+      <c r="AA41" s="13"/>
+      <c r="AB41" s="18"/>
+      <c r="AC41" s="18"/>
+      <c r="AD41" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE41" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="42" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A42" s="10"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F42" s="13">
+        <v>1</v>
+      </c>
+      <c r="G42" s="14">
+        <v>878</v>
+      </c>
+      <c r="H42" s="14">
+        <v>0</v>
+      </c>
+      <c r="I42" s="14">
+        <v>219.5</v>
+      </c>
+      <c r="J42" s="14">
+        <v>219.5</v>
+      </c>
+      <c r="K42" s="13">
+        <v>1</v>
+      </c>
+      <c r="L42" s="13">
+        <v>1</v>
+      </c>
+      <c r="M42" s="14">
+        <v>439</v>
+      </c>
+      <c r="N42" s="14">
+        <v>-439</v>
+      </c>
+      <c r="O42" s="14">
+        <v>8</v>
+      </c>
+      <c r="P42" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q42" s="15">
+        <v>0.97955654604444165</v>
+      </c>
+      <c r="R42" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S42" s="15">
+        <v>4</v>
+      </c>
+      <c r="T42" s="15">
+        <v>8347.1144379084508</v>
+      </c>
+      <c r="U42" s="15">
+        <v>0</v>
+      </c>
+      <c r="V42" s="13">
+        <v>0</v>
+      </c>
+      <c r="W42" s="15">
+        <v>0</v>
+      </c>
+      <c r="X42" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y42" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z42" s="13"/>
+      <c r="AA42" s="13"/>
+      <c r="AB42" s="18"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE42" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A43" s="10"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F43" s="13">
+        <v>1</v>
+      </c>
+      <c r="G43" s="14">
+        <v>1120.9999999900001</v>
+      </c>
+      <c r="H43" s="14">
+        <v>0</v>
+      </c>
+      <c r="I43" s="14">
+        <v>280.25</v>
+      </c>
+      <c r="J43" s="14">
+        <v>280.25</v>
+      </c>
+      <c r="K43" s="13">
+        <v>1</v>
+      </c>
+      <c r="L43" s="13">
+        <v>1</v>
+      </c>
+      <c r="M43" s="14">
+        <v>560.5</v>
+      </c>
+      <c r="N43" s="14">
+        <v>-560.5</v>
+      </c>
+      <c r="O43" s="14">
+        <v>8</v>
+      </c>
+      <c r="P43" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q43" s="15">
+        <v>0.76721734829142907</v>
+      </c>
+      <c r="R43" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S43" s="15">
+        <v>4</v>
+      </c>
+      <c r="T43" s="15">
+        <v>10657.30670251925</v>
+      </c>
+      <c r="U43" s="15">
+        <v>0</v>
+      </c>
+      <c r="V43" s="13">
+        <v>0</v>
+      </c>
+      <c r="W43" s="15">
+        <v>0</v>
+      </c>
+      <c r="X43" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y43" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z43" s="13"/>
+      <c r="AA43" s="13"/>
+      <c r="AB43" s="18"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE43" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A44" s="10"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="13">
+        <v>1</v>
+      </c>
+      <c r="G44" s="14">
+        <v>1724.69999998</v>
+      </c>
+      <c r="H44" s="14">
+        <v>0</v>
+      </c>
+      <c r="I44" s="14">
+        <v>431.17500000000001</v>
+      </c>
+      <c r="J44" s="14">
+        <v>431.17500000000001</v>
+      </c>
+      <c r="K44" s="13">
+        <v>1</v>
+      </c>
+      <c r="L44" s="13">
+        <v>1</v>
+      </c>
+      <c r="M44" s="14">
+        <v>862.35</v>
+      </c>
+      <c r="N44" s="14">
+        <v>-862.35</v>
+      </c>
+      <c r="O44" s="14">
+        <v>8</v>
+      </c>
+      <c r="P44" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q44" s="15">
+        <v>0.49866681013335257</v>
+      </c>
+      <c r="R44" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S44" s="15">
+        <v>4</v>
+      </c>
+      <c r="T44" s="15">
+        <v>16396.660900790161</v>
+      </c>
+      <c r="U44" s="15">
+        <v>0</v>
+      </c>
+      <c r="V44" s="13">
+        <v>0</v>
+      </c>
+      <c r="W44" s="15">
+        <v>0</v>
+      </c>
+      <c r="X44" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y44" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z44" s="13"/>
+      <c r="AA44" s="13"/>
+      <c r="AB44" s="18"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE44" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A45" s="10"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D45" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F45" s="13">
+        <v>1</v>
+      </c>
+      <c r="G45" s="14">
+        <v>7.8866666666666596</v>
+      </c>
+      <c r="H45" s="14">
+        <v>0</v>
+      </c>
+      <c r="I45" s="14">
+        <v>1.972</v>
+      </c>
+      <c r="J45" s="14">
+        <v>1.972</v>
+      </c>
+      <c r="K45" s="13">
+        <v>1</v>
+      </c>
+      <c r="L45" s="13">
+        <v>1</v>
+      </c>
+      <c r="M45" s="14">
+        <v>3.9430000000000001</v>
+      </c>
+      <c r="N45" s="14">
+        <v>-3.9430000000000001</v>
+      </c>
+      <c r="O45" s="14">
+        <v>8</v>
+      </c>
+      <c r="P45" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q45" s="15">
+        <v>109.05122325786398</v>
+      </c>
+      <c r="R45" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S45" s="15">
+        <v>4</v>
+      </c>
+      <c r="T45" s="15">
+        <v>74.978256492374243</v>
+      </c>
+      <c r="U45" s="15">
+        <v>0</v>
+      </c>
+      <c r="V45" s="13">
+        <v>0</v>
+      </c>
+      <c r="W45" s="15">
+        <v>0</v>
+      </c>
+      <c r="X45" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y45" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z45" s="13"/>
+      <c r="AA45" s="13"/>
+      <c r="AB45" s="18"/>
+      <c r="AC45" s="18"/>
+      <c r="AD45" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE45" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A46" s="10"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46" s="13">
+        <v>1</v>
+      </c>
+      <c r="G46" s="14">
+        <v>41.16</v>
+      </c>
+      <c r="H46" s="14">
+        <v>0</v>
+      </c>
+      <c r="I46" s="14">
+        <v>10.29</v>
+      </c>
+      <c r="J46" s="14">
+        <v>10.29</v>
+      </c>
+      <c r="K46" s="13">
+        <v>1</v>
+      </c>
+      <c r="L46" s="13">
+        <v>1</v>
+      </c>
+      <c r="M46" s="14">
+        <v>20.58</v>
+      </c>
+      <c r="N46" s="14">
+        <v>-20.58</v>
+      </c>
+      <c r="O46" s="14">
+        <v>8</v>
+      </c>
+      <c r="P46" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q46" s="15">
+        <v>20.895302415622449</v>
+      </c>
+      <c r="R46" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S46" s="15">
+        <v>4</v>
+      </c>
+      <c r="T46" s="15">
+        <v>391.30664039215463</v>
+      </c>
+      <c r="U46" s="15">
+        <v>0</v>
+      </c>
+      <c r="V46" s="13">
+        <v>0</v>
+      </c>
+      <c r="W46" s="15">
+        <v>0</v>
+      </c>
+      <c r="X46" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y46" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z46" s="13"/>
+      <c r="AA46" s="13"/>
+      <c r="AB46" s="18"/>
+      <c r="AC46" s="18"/>
+      <c r="AD46" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE46" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A47" s="10"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D47" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47" s="13">
+        <v>1</v>
+      </c>
+      <c r="G47" s="14">
+        <v>199</v>
+      </c>
+      <c r="H47" s="14">
+        <v>0</v>
+      </c>
+      <c r="I47" s="14">
+        <v>49.75</v>
+      </c>
+      <c r="J47" s="14">
+        <v>49.75</v>
+      </c>
+      <c r="K47" s="13">
+        <v>1</v>
+      </c>
+      <c r="L47" s="13">
+        <v>1</v>
+      </c>
+      <c r="M47" s="14">
+        <v>99.5</v>
+      </c>
+      <c r="N47" s="14">
+        <v>-99.5</v>
+      </c>
+      <c r="O47" s="14">
+        <v>8</v>
+      </c>
+      <c r="P47" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q47" s="15">
+        <v>4.3218625498845222</v>
+      </c>
+      <c r="R47" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S47" s="15">
+        <v>4</v>
+      </c>
+      <c r="T47" s="15">
+        <v>1891.8858464052182</v>
+      </c>
+      <c r="U47" s="15">
+        <v>0</v>
+      </c>
+      <c r="V47" s="13">
+        <v>0</v>
+      </c>
+      <c r="W47" s="15">
+        <v>0</v>
+      </c>
+      <c r="X47" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y47" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z47" s="13"/>
+      <c r="AA47" s="13"/>
+      <c r="AB47" s="18"/>
+      <c r="AC47" s="18"/>
+      <c r="AD47" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE47" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A48" s="10"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="F48" s="13">
+        <v>1</v>
+      </c>
+      <c r="G48" s="14">
+        <v>147.762</v>
+      </c>
+      <c r="H48" s="14">
+        <v>0</v>
+      </c>
+      <c r="I48" s="14">
+        <v>36.941000000000003</v>
+      </c>
+      <c r="J48" s="14">
+        <v>36.941000000000003</v>
+      </c>
+      <c r="K48" s="13">
+        <v>1</v>
+      </c>
+      <c r="L48" s="13">
+        <v>1</v>
+      </c>
+      <c r="M48" s="14">
+        <v>73.881</v>
+      </c>
+      <c r="N48" s="14">
+        <v>-73.881</v>
+      </c>
+      <c r="O48" s="14">
+        <v>8</v>
+      </c>
+      <c r="P48" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q48" s="15">
+        <v>5.8205130373642744</v>
+      </c>
+      <c r="R48" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S48" s="15">
+        <v>4</v>
+      </c>
+      <c r="T48" s="15">
+        <v>1404.7680222941101</v>
+      </c>
+      <c r="U48" s="15">
+        <v>0</v>
+      </c>
+      <c r="V48" s="13">
+        <v>0</v>
+      </c>
+      <c r="W48" s="15">
+        <v>0</v>
+      </c>
+      <c r="X48" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y48" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z48" s="13"/>
+      <c r="AA48" s="13"/>
+      <c r="AB48" s="18"/>
+      <c r="AC48" s="18"/>
+      <c r="AD48" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE48" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A49" s="10"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F49" s="13">
+        <v>1</v>
+      </c>
+      <c r="G49" s="14">
+        <v>156</v>
+      </c>
+      <c r="H49" s="14">
+        <v>0</v>
+      </c>
+      <c r="I49" s="14">
+        <v>39</v>
+      </c>
+      <c r="J49" s="14">
+        <v>39</v>
+      </c>
+      <c r="K49" s="13">
+        <v>1</v>
+      </c>
+      <c r="L49" s="13">
+        <v>1</v>
+      </c>
+      <c r="M49" s="14">
+        <v>78</v>
+      </c>
+      <c r="N49" s="14">
+        <v>-78</v>
+      </c>
+      <c r="O49" s="14">
+        <v>8</v>
+      </c>
+      <c r="P49" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q49" s="15">
+        <v>5.5131451758142305</v>
+      </c>
+      <c r="R49" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S49" s="15">
+        <v>4</v>
+      </c>
+      <c r="T49" s="15">
+        <v>1483.0863921568546</v>
+      </c>
+      <c r="U49" s="15">
+        <v>0</v>
+      </c>
+      <c r="V49" s="13">
+        <v>0</v>
+      </c>
+      <c r="W49" s="15">
+        <v>0</v>
+      </c>
+      <c r="X49" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y49" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z49" s="13"/>
+      <c r="AA49" s="13"/>
+      <c r="AB49" s="18"/>
+      <c r="AC49" s="18"/>
+      <c r="AD49" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE49" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A50" s="10"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F50" s="13">
+        <v>1</v>
+      </c>
+      <c r="G50" s="14">
+        <v>690.00000009999985</v>
+      </c>
+      <c r="H50" s="14">
+        <v>0</v>
+      </c>
+      <c r="I50" s="14">
+        <v>172.5</v>
+      </c>
+      <c r="J50" s="14">
+        <v>172.5</v>
+      </c>
+      <c r="K50" s="13">
+        <v>1</v>
+      </c>
+      <c r="L50" s="13">
+        <v>1</v>
+      </c>
+      <c r="M50" s="14">
+        <v>345</v>
+      </c>
+      <c r="N50" s="14">
+        <v>-345</v>
+      </c>
+      <c r="O50" s="14">
+        <v>8</v>
+      </c>
+      <c r="P50" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q50" s="15">
+        <v>1.246450213481703</v>
+      </c>
+      <c r="R50" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S50" s="15">
+        <v>4</v>
+      </c>
+      <c r="T50" s="15">
+        <v>6559.8051970290899</v>
+      </c>
+      <c r="U50" s="15">
+        <v>0</v>
+      </c>
+      <c r="V50" s="13">
+        <v>0</v>
+      </c>
+      <c r="W50" s="15">
+        <v>0</v>
+      </c>
+      <c r="X50" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y50" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z50" s="13"/>
+      <c r="AA50" s="13"/>
+      <c r="AB50" s="18"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE50" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A51" s="10"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F51" s="13">
+        <v>1</v>
+      </c>
+      <c r="G51" s="14">
+        <v>233.00000003</v>
+      </c>
+      <c r="H51" s="14">
+        <v>0</v>
+      </c>
+      <c r="I51" s="14">
+        <v>58.25</v>
+      </c>
+      <c r="J51" s="14">
+        <v>58.25</v>
+      </c>
+      <c r="K51" s="13">
+        <v>1</v>
+      </c>
+      <c r="L51" s="13">
+        <v>1</v>
+      </c>
+      <c r="M51" s="14">
+        <v>116.5</v>
+      </c>
+      <c r="N51" s="14">
+        <v>-116.5</v>
+      </c>
+      <c r="O51" s="14">
+        <v>8</v>
+      </c>
+      <c r="P51" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q51" s="15">
+        <v>3.6912044949196732</v>
+      </c>
+      <c r="R51" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S51" s="15">
+        <v>4</v>
+      </c>
+      <c r="T51" s="15">
+        <v>2215.122624468203</v>
+      </c>
+      <c r="U51" s="15">
+        <v>0</v>
+      </c>
+      <c r="V51" s="13">
+        <v>0</v>
+      </c>
+      <c r="W51" s="15">
+        <v>0</v>
+      </c>
+      <c r="X51" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y51" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z51" s="13"/>
+      <c r="AA51" s="13"/>
+      <c r="AB51" s="18"/>
+      <c r="AC51" s="18"/>
+      <c r="AD51" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE51" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A52" s="10"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F52" s="13">
+        <v>1</v>
+      </c>
+      <c r="G52" s="14">
+        <v>531.202</v>
+      </c>
+      <c r="H52" s="14">
+        <v>0</v>
+      </c>
+      <c r="I52" s="14">
+        <v>132.80099999999999</v>
+      </c>
+      <c r="J52" s="14">
+        <v>132.80099999999999</v>
+      </c>
+      <c r="K52" s="13">
+        <v>1</v>
+      </c>
+      <c r="L52" s="13">
+        <v>1</v>
+      </c>
+      <c r="M52" s="14">
+        <v>265.601</v>
+      </c>
+      <c r="N52" s="14">
+        <v>-265.601</v>
+      </c>
+      <c r="O52" s="14">
+        <v>8</v>
+      </c>
+      <c r="P52" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q52" s="15">
+        <v>1.6190651530435125</v>
+      </c>
+      <c r="R52" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S52" s="15">
+        <v>4</v>
+      </c>
+      <c r="T52" s="15">
+        <v>5050.1183185032396</v>
+      </c>
+      <c r="U52" s="15">
+        <v>0</v>
+      </c>
+      <c r="V52" s="13">
+        <v>0</v>
+      </c>
+      <c r="W52" s="15">
+        <v>0</v>
+      </c>
+      <c r="X52" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y52" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z52" s="13"/>
+      <c r="AA52" s="13"/>
+      <c r="AB52" s="18"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE52" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A53" s="10"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F53" s="13">
+        <v>1</v>
+      </c>
+      <c r="G53" s="14">
+        <v>218</v>
+      </c>
+      <c r="H53" s="14">
+        <v>0</v>
+      </c>
+      <c r="I53" s="14">
+        <v>54.5</v>
+      </c>
+      <c r="J53" s="14">
+        <v>54.5</v>
+      </c>
+      <c r="K53" s="13">
+        <v>1</v>
+      </c>
+      <c r="L53" s="13">
+        <v>1</v>
+      </c>
+      <c r="M53" s="14">
+        <v>109</v>
+      </c>
+      <c r="N53" s="14">
+        <v>-109</v>
+      </c>
+      <c r="O53" s="14">
+        <v>8</v>
+      </c>
+      <c r="P53" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q53" s="15">
+        <v>3.9451864560872476</v>
+      </c>
+      <c r="R53" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S53" s="15">
+        <v>4</v>
+      </c>
+      <c r="T53" s="15">
+        <v>2072.5181633986813</v>
+      </c>
+      <c r="U53" s="15">
+        <v>0</v>
+      </c>
+      <c r="V53" s="13">
+        <v>0</v>
+      </c>
+      <c r="W53" s="15">
+        <v>0</v>
+      </c>
+      <c r="X53" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y53" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z53" s="13"/>
+      <c r="AA53" s="13"/>
+      <c r="AB53" s="18"/>
+      <c r="AC53" s="18"/>
+      <c r="AD53" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE53" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A54" s="10"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="D54" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F54" s="13">
+        <v>1</v>
+      </c>
+      <c r="G54" s="14">
+        <v>331</v>
+      </c>
+      <c r="H54" s="14">
+        <v>0</v>
+      </c>
+      <c r="I54" s="14">
+        <v>82.75</v>
+      </c>
+      <c r="J54" s="14">
+        <v>82.75</v>
+      </c>
+      <c r="K54" s="13">
+        <v>1</v>
+      </c>
+      <c r="L54" s="13">
+        <v>1</v>
+      </c>
+      <c r="M54" s="14">
+        <v>165.5</v>
+      </c>
+      <c r="N54" s="14">
+        <v>-165.5</v>
+      </c>
+      <c r="O54" s="14">
+        <v>8</v>
+      </c>
+      <c r="P54" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q54" s="15">
+        <v>2.5983403245529302</v>
+      </c>
+      <c r="R54" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S54" s="15">
+        <v>4</v>
+      </c>
+      <c r="T54" s="15">
+        <v>3146.8051013071718</v>
+      </c>
+      <c r="U54" s="15">
+        <v>0</v>
+      </c>
+      <c r="V54" s="13">
+        <v>0</v>
+      </c>
+      <c r="W54" s="15">
+        <v>0</v>
+      </c>
+      <c r="X54" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y54" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z54" s="13"/>
+      <c r="AA54" s="13"/>
+      <c r="AB54" s="18"/>
+      <c r="AC54" s="18"/>
+      <c r="AD54" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE54" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A55" s="10"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="13">
+        <v>1</v>
+      </c>
+      <c r="G55" s="14">
+        <v>90.11</v>
+      </c>
+      <c r="H55" s="14">
+        <v>0</v>
+      </c>
+      <c r="I55" s="14">
+        <v>22.527999999999999</v>
+      </c>
+      <c r="J55" s="14">
+        <v>22.527999999999999</v>
+      </c>
+      <c r="K55" s="13">
+        <v>1</v>
+      </c>
+      <c r="L55" s="13">
+        <v>1</v>
+      </c>
+      <c r="M55" s="14">
+        <v>45.055</v>
+      </c>
+      <c r="N55" s="14">
+        <v>-45.055</v>
+      </c>
+      <c r="O55" s="14">
+        <v>8</v>
+      </c>
+      <c r="P55" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q55" s="15">
+        <v>9.544452862357339</v>
+      </c>
+      <c r="R55" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S55" s="15">
+        <v>4</v>
+      </c>
+      <c r="T55" s="15">
+        <v>856.67253075162921</v>
+      </c>
+      <c r="U55" s="15">
+        <v>0</v>
+      </c>
+      <c r="V55" s="13">
+        <v>0</v>
+      </c>
+      <c r="W55" s="15">
+        <v>0</v>
+      </c>
+      <c r="X55" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y55" s="17">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="Z55" s="13"/>
+      <c r="AA55" s="13"/>
+      <c r="AB55" s="18"/>
+      <c r="AC55" s="18"/>
+      <c r="AD55" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE55" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A56" s="10"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D56" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" s="13">
+        <v>1</v>
+      </c>
+      <c r="G56" s="14">
+        <v>244</v>
+      </c>
+      <c r="H56" s="14">
+        <v>0</v>
+      </c>
+      <c r="I56" s="14">
+        <v>61</v>
+      </c>
+      <c r="J56" s="14">
+        <v>61</v>
+      </c>
+      <c r="K56" s="13">
+        <v>1</v>
+      </c>
+      <c r="L56" s="13">
+        <v>1</v>
+      </c>
+      <c r="M56" s="14">
+        <v>122</v>
+      </c>
+      <c r="N56" s="14">
+        <v>-122</v>
+      </c>
+      <c r="O56" s="14">
+        <v>8</v>
+      </c>
+      <c r="P56" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q56" s="15">
+        <v>9.3372125439910967</v>
+      </c>
+      <c r="R56" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S56" s="15">
+        <v>4</v>
+      </c>
+      <c r="T56" s="15">
+        <v>400.52360784313504</v>
+      </c>
+      <c r="U56" s="15">
+        <v>0</v>
+      </c>
+      <c r="V56" s="13">
+        <v>0</v>
+      </c>
+      <c r="W56" s="15">
+        <v>0</v>
+      </c>
+      <c r="X56" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y56" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z56" s="13"/>
+      <c r="AA56" s="13"/>
+      <c r="AB56" s="18"/>
+      <c r="AC56" s="18"/>
+      <c r="AD56" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE56" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A57" s="10"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F57" s="13">
+        <v>1</v>
+      </c>
+      <c r="G57" s="14">
+        <v>20</v>
+      </c>
+      <c r="H57" s="14">
+        <v>0</v>
+      </c>
+      <c r="I57" s="14">
+        <v>5</v>
+      </c>
+      <c r="J57" s="14">
+        <v>5</v>
+      </c>
+      <c r="K57" s="13">
+        <v>1</v>
+      </c>
+      <c r="L57" s="13">
+        <v>1</v>
+      </c>
+      <c r="M57" s="14">
+        <v>10</v>
+      </c>
+      <c r="N57" s="14">
+        <v>-10</v>
+      </c>
+      <c r="O57" s="14">
+        <v>8</v>
+      </c>
+      <c r="P57" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q57" s="15">
+        <v>9.2369310216627643</v>
+      </c>
+      <c r="R57" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S57" s="15">
+        <v>4</v>
+      </c>
+      <c r="T57" s="15">
+        <v>32.829803921568441</v>
+      </c>
+      <c r="U57" s="15">
+        <v>0</v>
+      </c>
+      <c r="V57" s="13">
+        <v>0</v>
+      </c>
+      <c r="W57" s="15">
+        <v>0</v>
+      </c>
+      <c r="X57" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y57" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z57" s="13"/>
+      <c r="AA57" s="13"/>
+      <c r="AB57" s="18"/>
+      <c r="AC57" s="18"/>
+      <c r="AD57" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE57" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="58" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A58" s="10"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D58" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="13">
+        <v>1</v>
+      </c>
+      <c r="G58" s="14">
+        <v>3831</v>
+      </c>
+      <c r="H58" s="14">
+        <v>0</v>
+      </c>
+      <c r="I58" s="14">
+        <v>957.75</v>
+      </c>
+      <c r="J58" s="14">
+        <v>957.75</v>
+      </c>
+      <c r="K58" s="13">
+        <v>1</v>
+      </c>
+      <c r="L58" s="13">
+        <v>1</v>
+      </c>
+      <c r="M58" s="14">
+        <v>1915.5</v>
+      </c>
+      <c r="N58" s="14">
+        <v>-1915.5</v>
+      </c>
+      <c r="O58" s="14">
+        <v>8</v>
+      </c>
+      <c r="P58" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q58" s="15">
+        <v>9.1387806548402928</v>
+      </c>
+      <c r="R58" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S58" s="15">
+        <v>4</v>
+      </c>
+      <c r="T58" s="15">
+        <v>6288.5489411764356</v>
+      </c>
+      <c r="U58" s="15">
+        <v>0</v>
+      </c>
+      <c r="V58" s="13">
+        <v>0</v>
+      </c>
+      <c r="W58" s="15">
+        <v>0</v>
+      </c>
+      <c r="X58" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y58" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z58" s="13"/>
+      <c r="AA58" s="13"/>
+      <c r="AB58" s="18"/>
+      <c r="AC58" s="18"/>
+      <c r="AD58" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE58" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A59" s="10"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F59" s="13">
+        <v>1</v>
+      </c>
+      <c r="G59" s="14">
+        <v>88.508333350000001</v>
+      </c>
+      <c r="H59" s="14">
+        <v>0</v>
+      </c>
+      <c r="I59" s="14">
+        <v>22.126999999999999</v>
+      </c>
+      <c r="J59" s="14">
+        <v>22.126999999999999</v>
+      </c>
+      <c r="K59" s="13">
+        <v>1</v>
+      </c>
+      <c r="L59" s="13">
+        <v>1</v>
+      </c>
+      <c r="M59" s="14">
+        <v>44.253999999999998</v>
+      </c>
+      <c r="N59" s="14">
+        <v>-44.253999999999998</v>
+      </c>
+      <c r="O59" s="14">
+        <v>8</v>
+      </c>
+      <c r="P59" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q59" s="15">
+        <v>9.042694221711912</v>
+      </c>
+      <c r="R59" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S59" s="15">
+        <v>4</v>
+      </c>
+      <c r="T59" s="15">
+        <v>145.28556146526586</v>
+      </c>
+      <c r="U59" s="15">
+        <v>0</v>
+      </c>
+      <c r="V59" s="13">
+        <v>0</v>
+      </c>
+      <c r="W59" s="15">
+        <v>0</v>
+      </c>
+      <c r="X59" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y59" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z59" s="13"/>
+      <c r="AA59" s="13"/>
+      <c r="AB59" s="18"/>
+      <c r="AC59" s="18"/>
+      <c r="AD59" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE59" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D60" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F60" s="13">
+        <v>1</v>
+      </c>
+      <c r="G60" s="14">
+        <v>13.9266666666667</v>
+      </c>
+      <c r="H60" s="14">
+        <v>0</v>
+      </c>
+      <c r="I60" s="14">
+        <v>3.4820000000000002</v>
+      </c>
+      <c r="J60" s="14">
+        <v>3.4820000000000002</v>
+      </c>
+      <c r="K60" s="13">
+        <v>1</v>
+      </c>
+      <c r="L60" s="13">
+        <v>1</v>
+      </c>
+      <c r="M60" s="14">
+        <v>6.9630000000000001</v>
+      </c>
+      <c r="N60" s="14">
+        <v>-6.9630000000000001</v>
+      </c>
+      <c r="O60" s="14">
+        <v>8</v>
+      </c>
+      <c r="P60" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q60" s="15">
+        <v>8.9486072981689713</v>
+      </c>
+      <c r="R60" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S60" s="15">
+        <v>4</v>
+      </c>
+      <c r="T60" s="15">
+        <v>22.860486797385548</v>
+      </c>
+      <c r="U60" s="15">
+        <v>0</v>
+      </c>
+      <c r="V60" s="13">
+        <v>0</v>
+      </c>
+      <c r="W60" s="15">
+        <v>0</v>
+      </c>
+      <c r="X60" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y60" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z60" s="13"/>
+      <c r="AA60" s="13"/>
+      <c r="AB60" s="18"/>
+      <c r="AC60" s="18"/>
+      <c r="AD60" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE60" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A61" s="10"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F61" s="13">
+        <v>1</v>
+      </c>
+      <c r="G61" s="14">
+        <v>437.00000010000002</v>
+      </c>
+      <c r="H61" s="14">
+        <v>0</v>
+      </c>
+      <c r="I61" s="14">
+        <v>109.25</v>
+      </c>
+      <c r="J61" s="14">
+        <v>109.25</v>
+      </c>
+      <c r="K61" s="13">
+        <v>1</v>
+      </c>
+      <c r="L61" s="13">
+        <v>1</v>
+      </c>
+      <c r="M61" s="14">
+        <v>218.5</v>
+      </c>
+      <c r="N61" s="14">
+        <v>-218.5</v>
+      </c>
+      <c r="O61" s="14">
+        <v>8</v>
+      </c>
+      <c r="P61" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q61" s="15">
+        <v>8.8564581137577996</v>
+      </c>
+      <c r="R61" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S61" s="15">
+        <v>4</v>
+      </c>
+      <c r="T61" s="15">
+        <v>717.33121585041954</v>
+      </c>
+      <c r="U61" s="15">
+        <v>0</v>
+      </c>
+      <c r="V61" s="13">
+        <v>0</v>
+      </c>
+      <c r="W61" s="15">
+        <v>0</v>
+      </c>
+      <c r="X61" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y61" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z61" s="13"/>
+      <c r="AA61" s="13"/>
+      <c r="AB61" s="18"/>
+      <c r="AC61" s="18"/>
+      <c r="AD61" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE61" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A62" s="10"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="D62" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F62" s="13">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14">
+        <v>3130</v>
+      </c>
+      <c r="H62" s="14">
+        <v>0</v>
+      </c>
+      <c r="I62" s="14">
+        <v>782.5</v>
+      </c>
+      <c r="J62" s="14">
+        <v>782.5</v>
+      </c>
+      <c r="K62" s="13">
+        <v>1</v>
+      </c>
+      <c r="L62" s="13">
+        <v>1</v>
+      </c>
+      <c r="M62" s="14">
+        <v>1565</v>
+      </c>
+      <c r="N62" s="14">
+        <v>-1565</v>
+      </c>
+      <c r="O62" s="14">
+        <v>8</v>
+      </c>
+      <c r="P62" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q62" s="15">
+        <v>8.7661874164409337</v>
+      </c>
+      <c r="R62" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S62" s="15">
+        <v>4</v>
+      </c>
+      <c r="T62" s="15">
+        <v>5137.8643137254621</v>
+      </c>
+      <c r="U62" s="15">
+        <v>0</v>
+      </c>
+      <c r="V62" s="13">
+        <v>0</v>
+      </c>
+      <c r="W62" s="15">
+        <v>0</v>
+      </c>
+      <c r="X62" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y62" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z62" s="13"/>
+      <c r="AA62" s="13"/>
+      <c r="AB62" s="18"/>
+      <c r="AC62" s="18"/>
+      <c r="AD62" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE62" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A63" s="10"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F63" s="13">
+        <v>1</v>
+      </c>
+      <c r="G63" s="14">
+        <v>547.80000013999995</v>
+      </c>
+      <c r="H63" s="14">
+        <v>0</v>
+      </c>
+      <c r="I63" s="14">
+        <v>136.94999999999999</v>
+      </c>
+      <c r="J63" s="14">
+        <v>136.94999999999999</v>
+      </c>
+      <c r="K63" s="13">
+        <v>1</v>
+      </c>
+      <c r="L63" s="13">
+        <v>1</v>
+      </c>
+      <c r="M63" s="14">
+        <v>273.89999999999998</v>
+      </c>
+      <c r="N63" s="14">
+        <v>-273.89999999999998</v>
+      </c>
+      <c r="O63" s="14">
+        <v>8</v>
+      </c>
+      <c r="P63" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q63" s="15">
+        <v>8.6777383455455546</v>
+      </c>
+      <c r="R63" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S63" s="15">
+        <v>4</v>
+      </c>
+      <c r="T63" s="15">
+        <v>899.20832964156818</v>
+      </c>
+      <c r="U63" s="15">
+        <v>0</v>
+      </c>
+      <c r="V63" s="13">
+        <v>0</v>
+      </c>
+      <c r="W63" s="15">
+        <v>0</v>
+      </c>
+      <c r="X63" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y63" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z63" s="13"/>
+      <c r="AA63" s="13"/>
+      <c r="AB63" s="18"/>
+      <c r="AC63" s="18"/>
+      <c r="AD63" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE63" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A64" s="10"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D64" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F64" s="13">
+        <v>1</v>
+      </c>
+      <c r="G64" s="14">
+        <v>3600</v>
+      </c>
+      <c r="H64" s="14">
+        <v>0</v>
+      </c>
+      <c r="I64" s="14">
+        <v>900</v>
+      </c>
+      <c r="J64" s="14">
+        <v>900</v>
+      </c>
+      <c r="K64" s="13">
+        <v>1</v>
+      </c>
+      <c r="L64" s="13">
+        <v>1</v>
+      </c>
+      <c r="M64" s="14">
+        <v>1800</v>
+      </c>
+      <c r="N64" s="14">
+        <v>-1800</v>
+      </c>
+      <c r="O64" s="14">
+        <v>8</v>
+      </c>
+      <c r="P64" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q64" s="15">
+        <v>8.5910563123266392</v>
+      </c>
+      <c r="R64" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S64" s="15">
+        <v>4</v>
+      </c>
+      <c r="T64" s="15">
+        <v>5909.3647058823199</v>
+      </c>
+      <c r="U64" s="15">
+        <v>0</v>
+      </c>
+      <c r="V64" s="13">
+        <v>0</v>
+      </c>
+      <c r="W64" s="15">
+        <v>0</v>
+      </c>
+      <c r="X64" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y64" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z64" s="13"/>
+      <c r="AA64" s="13"/>
+      <c r="AB64" s="18"/>
+      <c r="AC64" s="18"/>
+      <c r="AD64" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE64" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A65" s="10"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F65" s="13">
+        <v>1</v>
+      </c>
+      <c r="G65" s="14">
+        <v>1050.8999997999999</v>
+      </c>
+      <c r="H65" s="14">
+        <v>0</v>
+      </c>
+      <c r="I65" s="14">
+        <v>262.72500000000002</v>
+      </c>
+      <c r="J65" s="14">
+        <v>262.72500000000002</v>
+      </c>
+      <c r="K65" s="13">
+        <v>1</v>
+      </c>
+      <c r="L65" s="13">
+        <v>1</v>
+      </c>
+      <c r="M65" s="14">
+        <v>525.45000000000005</v>
+      </c>
+      <c r="N65" s="14">
+        <v>-525.45000000000005</v>
+      </c>
+      <c r="O65" s="14">
+        <v>8</v>
+      </c>
+      <c r="P65" s="15">
+        <v>14.620861006259339</v>
+      </c>
+      <c r="Q65" s="15">
+        <v>8.5060888876176435</v>
+      </c>
+      <c r="R65" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S65" s="15">
+        <v>4</v>
+      </c>
+      <c r="T65" s="15">
+        <v>1725.0420467305157</v>
+      </c>
+      <c r="U65" s="15">
+        <v>0</v>
+      </c>
+      <c r="V65" s="13">
+        <v>0</v>
+      </c>
+      <c r="W65" s="15">
+        <v>0</v>
+      </c>
+      <c r="X65" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y65" s="17">
+        <v>0.49</v>
+      </c>
+      <c r="Z65" s="13"/>
+      <c r="AA65" s="13"/>
+      <c r="AB65" s="18"/>
+      <c r="AC65" s="18"/>
+      <c r="AD65" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE65" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A66" s="10"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D66" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F66" s="13">
+        <v>1</v>
+      </c>
+      <c r="G66" s="14">
+        <v>6488.99999999997</v>
+      </c>
+      <c r="H66" s="14">
+        <v>0</v>
+      </c>
+      <c r="I66" s="14">
+        <v>1622.25</v>
+      </c>
+      <c r="J66" s="14">
+        <v>1622.25</v>
+      </c>
+      <c r="K66" s="13">
+        <v>1</v>
+      </c>
+      <c r="L66" s="13">
+        <v>1</v>
+      </c>
+      <c r="M66" s="14">
+        <v>3244.5</v>
+      </c>
+      <c r="N66" s="14">
+        <v>-3244.5</v>
+      </c>
+      <c r="O66" s="14">
+        <v>8</v>
+      </c>
+      <c r="P66" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q66" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R66" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S66" s="15">
+        <v>4</v>
+      </c>
+      <c r="T66" s="15">
+        <v>26784.410974999726</v>
+      </c>
+      <c r="U66" s="15">
+        <v>0</v>
+      </c>
+      <c r="V66" s="13">
+        <v>0</v>
+      </c>
+      <c r="W66" s="15">
+        <v>0</v>
+      </c>
+      <c r="X66" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y66" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z66" s="13"/>
+      <c r="AA66" s="13"/>
+      <c r="AB66" s="18"/>
+      <c r="AC66" s="18"/>
+      <c r="AD66" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE66" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A67" s="10"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="13">
+        <v>1</v>
+      </c>
+      <c r="G67" s="14">
+        <v>2296</v>
+      </c>
+      <c r="H67" s="14">
+        <v>0</v>
+      </c>
+      <c r="I67" s="14">
+        <v>574</v>
+      </c>
+      <c r="J67" s="14">
+        <v>574</v>
+      </c>
+      <c r="K67" s="13">
+        <v>1</v>
+      </c>
+      <c r="L67" s="13">
+        <v>1</v>
+      </c>
+      <c r="M67" s="14">
+        <v>1148</v>
+      </c>
+      <c r="N67" s="14">
+        <v>-1148</v>
+      </c>
+      <c r="O67" s="14">
+        <v>8</v>
+      </c>
+      <c r="P67" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q67" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R67" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S67" s="15">
+        <v>4</v>
+      </c>
+      <c r="T67" s="15">
+        <v>9477.1162888888375</v>
+      </c>
+      <c r="U67" s="15">
+        <v>0</v>
+      </c>
+      <c r="V67" s="13">
+        <v>0</v>
+      </c>
+      <c r="W67" s="15">
+        <v>0</v>
+      </c>
+      <c r="X67" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y67" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z67" s="13"/>
+      <c r="AA67" s="13"/>
+      <c r="AB67" s="18"/>
+      <c r="AC67" s="18"/>
+      <c r="AD67" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE67" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A68" s="10"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D68" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="13">
+        <v>1</v>
+      </c>
+      <c r="G68" s="14">
+        <v>1771</v>
+      </c>
+      <c r="H68" s="14">
+        <v>0</v>
+      </c>
+      <c r="I68" s="14">
+        <v>442.75</v>
+      </c>
+      <c r="J68" s="14">
+        <v>442.75</v>
+      </c>
+      <c r="K68" s="13">
+        <v>1</v>
+      </c>
+      <c r="L68" s="13">
+        <v>1</v>
+      </c>
+      <c r="M68" s="14">
+        <v>885.5</v>
+      </c>
+      <c r="N68" s="14">
+        <v>-885.5</v>
+      </c>
+      <c r="O68" s="14">
+        <v>8</v>
+      </c>
+      <c r="P68" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q68" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R68" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S68" s="15">
+        <v>4</v>
+      </c>
+      <c r="T68" s="15">
+        <v>7310.092747222182</v>
+      </c>
+      <c r="U68" s="15">
+        <v>0</v>
+      </c>
+      <c r="V68" s="13">
+        <v>0</v>
+      </c>
+      <c r="W68" s="15">
+        <v>0</v>
+      </c>
+      <c r="X68" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y68" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z68" s="13"/>
+      <c r="AA68" s="13"/>
+      <c r="AB68" s="18"/>
+      <c r="AC68" s="18"/>
+      <c r="AD68" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE68" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A69" s="10"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F69" s="13">
+        <v>1</v>
+      </c>
+      <c r="G69" s="14">
+        <v>4454</v>
+      </c>
+      <c r="H69" s="14">
+        <v>0</v>
+      </c>
+      <c r="I69" s="14">
+        <v>1113.5</v>
+      </c>
+      <c r="J69" s="14">
+        <v>1113.5</v>
+      </c>
+      <c r="K69" s="13">
+        <v>1</v>
+      </c>
+      <c r="L69" s="13">
+        <v>1</v>
+      </c>
+      <c r="M69" s="14">
+        <v>2227</v>
+      </c>
+      <c r="N69" s="14">
+        <v>-2227</v>
+      </c>
+      <c r="O69" s="14">
+        <v>8</v>
+      </c>
+      <c r="P69" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q69" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R69" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S69" s="15">
+        <v>4</v>
+      </c>
+      <c r="T69" s="15">
+        <v>18384.614961111009</v>
+      </c>
+      <c r="U69" s="15">
+        <v>0</v>
+      </c>
+      <c r="V69" s="13">
+        <v>0</v>
+      </c>
+      <c r="W69" s="15">
+        <v>0</v>
+      </c>
+      <c r="X69" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y69" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z69" s="13"/>
+      <c r="AA69" s="13"/>
+      <c r="AB69" s="18"/>
+      <c r="AC69" s="18"/>
+      <c r="AD69" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE69" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A70" s="10"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D70" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F70" s="13">
+        <v>1</v>
+      </c>
+      <c r="G70" s="14">
+        <v>2364.4675000000002</v>
+      </c>
+      <c r="H70" s="14">
+        <v>0</v>
+      </c>
+      <c r="I70" s="14">
+        <v>591.11699999999996</v>
+      </c>
+      <c r="J70" s="14">
+        <v>591.11699999999996</v>
+      </c>
+      <c r="K70" s="13">
+        <v>1</v>
+      </c>
+      <c r="L70" s="13">
+        <v>1</v>
+      </c>
+      <c r="M70" s="14">
+        <v>1182.2339999999999</v>
+      </c>
+      <c r="N70" s="14">
+        <v>-1182.2339999999999</v>
+      </c>
+      <c r="O70" s="14">
+        <v>8</v>
+      </c>
+      <c r="P70" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q70" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R70" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S70" s="15">
+        <v>4</v>
+      </c>
+      <c r="T70" s="15">
+        <v>9759.7271162013349</v>
+      </c>
+      <c r="U70" s="15">
+        <v>0</v>
+      </c>
+      <c r="V70" s="13">
+        <v>0</v>
+      </c>
+      <c r="W70" s="15">
+        <v>0</v>
+      </c>
+      <c r="X70" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y70" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z70" s="13"/>
+      <c r="AA70" s="13"/>
+      <c r="AB70" s="18"/>
+      <c r="AC70" s="18"/>
+      <c r="AD70" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE70" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A71" s="10"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F71" s="13">
+        <v>1</v>
+      </c>
+      <c r="G71" s="14">
+        <v>3229.0999999999899</v>
+      </c>
+      <c r="H71" s="14">
+        <v>0</v>
+      </c>
+      <c r="I71" s="14">
+        <v>807.27499999999998</v>
+      </c>
+      <c r="J71" s="14">
+        <v>807.27499999999998</v>
+      </c>
+      <c r="K71" s="13">
+        <v>1</v>
+      </c>
+      <c r="L71" s="13">
+        <v>1</v>
+      </c>
+      <c r="M71" s="14">
+        <v>1614.55</v>
+      </c>
+      <c r="N71" s="14">
+        <v>-1614.55</v>
+      </c>
+      <c r="O71" s="14">
+        <v>8</v>
+      </c>
+      <c r="P71" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q71" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R71" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S71" s="15">
+        <v>4</v>
+      </c>
+      <c r="T71" s="15">
+        <v>13328.639463610994</v>
+      </c>
+      <c r="U71" s="15">
+        <v>0</v>
+      </c>
+      <c r="V71" s="13">
+        <v>0</v>
+      </c>
+      <c r="W71" s="15">
+        <v>0</v>
+      </c>
+      <c r="X71" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y71" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z71" s="13"/>
+      <c r="AA71" s="13"/>
+      <c r="AB71" s="18"/>
+      <c r="AC71" s="18"/>
+      <c r="AD71" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE71" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A72" s="10"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="D72" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F72" s="13">
+        <v>1</v>
+      </c>
+      <c r="G72" s="14">
+        <v>377</v>
+      </c>
+      <c r="H72" s="14">
+        <v>0</v>
+      </c>
+      <c r="I72" s="14">
+        <v>94.25</v>
+      </c>
+      <c r="J72" s="14">
+        <v>94.25</v>
+      </c>
+      <c r="K72" s="13">
+        <v>1</v>
+      </c>
+      <c r="L72" s="13">
+        <v>1</v>
+      </c>
+      <c r="M72" s="14">
+        <v>188.5</v>
+      </c>
+      <c r="N72" s="14">
+        <v>-188.5</v>
+      </c>
+      <c r="O72" s="14">
+        <v>8</v>
+      </c>
+      <c r="P72" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q72" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R72" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S72" s="15">
+        <v>4</v>
+      </c>
+      <c r="T72" s="15">
+        <v>1556.1292861111026</v>
+      </c>
+      <c r="U72" s="15">
+        <v>0</v>
+      </c>
+      <c r="V72" s="13">
+        <v>0</v>
+      </c>
+      <c r="W72" s="15">
+        <v>0</v>
+      </c>
+      <c r="X72" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y72" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z72" s="13"/>
+      <c r="AA72" s="13"/>
+      <c r="AB72" s="18"/>
+      <c r="AC72" s="18"/>
+      <c r="AD72" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE72" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A73" s="10"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F73" s="13">
+        <v>1</v>
+      </c>
+      <c r="G73" s="14">
+        <v>16233</v>
+      </c>
+      <c r="H73" s="14">
+        <v>0</v>
+      </c>
+      <c r="I73" s="14">
+        <v>4058.25</v>
+      </c>
+      <c r="J73" s="14">
+        <v>4058.25</v>
+      </c>
+      <c r="K73" s="13">
+        <v>1</v>
+      </c>
+      <c r="L73" s="13">
+        <v>1</v>
+      </c>
+      <c r="M73" s="14">
+        <v>8116.5</v>
+      </c>
+      <c r="N73" s="14">
+        <v>-8116.5</v>
+      </c>
+      <c r="O73" s="14">
+        <v>8</v>
+      </c>
+      <c r="P73" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q73" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R73" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S73" s="15">
+        <v>4</v>
+      </c>
+      <c r="T73" s="15">
+        <v>67004.367908332963</v>
+      </c>
+      <c r="U73" s="15">
+        <v>0</v>
+      </c>
+      <c r="V73" s="13">
+        <v>0</v>
+      </c>
+      <c r="W73" s="15">
+        <v>0</v>
+      </c>
+      <c r="X73" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y73" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z73" s="13"/>
+      <c r="AA73" s="13"/>
+      <c r="AB73" s="18"/>
+      <c r="AC73" s="18"/>
+      <c r="AD73" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE73" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A74" s="10"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F74" s="13">
+        <v>1</v>
+      </c>
+      <c r="G74" s="14">
+        <v>1806</v>
+      </c>
+      <c r="H74" s="14">
+        <v>0</v>
+      </c>
+      <c r="I74" s="14">
+        <v>451.5</v>
+      </c>
+      <c r="J74" s="14">
+        <v>451.5</v>
+      </c>
+      <c r="K74" s="13">
+        <v>1</v>
+      </c>
+      <c r="L74" s="13">
+        <v>1</v>
+      </c>
+      <c r="M74" s="14">
+        <v>903</v>
+      </c>
+      <c r="N74" s="14">
+        <v>-903</v>
+      </c>
+      <c r="O74" s="14">
+        <v>8</v>
+      </c>
+      <c r="P74" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q74" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R74" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S74" s="15">
+        <v>4</v>
+      </c>
+      <c r="T74" s="15">
+        <v>7454.5609833332919</v>
+      </c>
+      <c r="U74" s="15">
+        <v>0</v>
+      </c>
+      <c r="V74" s="13">
+        <v>0</v>
+      </c>
+      <c r="W74" s="15">
+        <v>0</v>
+      </c>
+      <c r="X74" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y74" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z74" s="13"/>
+      <c r="AA74" s="13"/>
+      <c r="AB74" s="18"/>
+      <c r="AC74" s="18"/>
+      <c r="AD74" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE74" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A75" s="10"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F75" s="13">
+        <v>1</v>
+      </c>
+      <c r="G75" s="14">
+        <v>219</v>
+      </c>
+      <c r="H75" s="14">
+        <v>0</v>
+      </c>
+      <c r="I75" s="14">
+        <v>54.75</v>
+      </c>
+      <c r="J75" s="14">
+        <v>54.75</v>
+      </c>
+      <c r="K75" s="13">
+        <v>1</v>
+      </c>
+      <c r="L75" s="13">
+        <v>1</v>
+      </c>
+      <c r="M75" s="14">
+        <v>109.5</v>
+      </c>
+      <c r="N75" s="14">
+        <v>-109.5</v>
+      </c>
+      <c r="O75" s="14">
+        <v>8</v>
+      </c>
+      <c r="P75" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q75" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R75" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S75" s="15">
+        <v>4</v>
+      </c>
+      <c r="T75" s="15">
+        <v>903.95839166666167</v>
+      </c>
+      <c r="U75" s="15">
+        <v>0</v>
+      </c>
+      <c r="V75" s="13">
+        <v>0</v>
+      </c>
+      <c r="W75" s="15">
+        <v>0</v>
+      </c>
+      <c r="X75" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y75" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z75" s="13"/>
+      <c r="AA75" s="13"/>
+      <c r="AB75" s="18"/>
+      <c r="AC75" s="18"/>
+      <c r="AD75" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE75" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A76" s="10"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F76" s="13">
+        <v>1</v>
+      </c>
+      <c r="G76" s="14">
+        <v>386</v>
+      </c>
+      <c r="H76" s="14">
+        <v>0</v>
+      </c>
+      <c r="I76" s="14">
+        <v>96.5</v>
+      </c>
+      <c r="J76" s="14">
+        <v>96.5</v>
+      </c>
+      <c r="K76" s="13">
+        <v>1</v>
+      </c>
+      <c r="L76" s="13">
+        <v>1</v>
+      </c>
+      <c r="M76" s="14">
+        <v>193</v>
+      </c>
+      <c r="N76" s="14">
+        <v>-193</v>
+      </c>
+      <c r="O76" s="14">
+        <v>8</v>
+      </c>
+      <c r="P76" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q76" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R76" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S76" s="15">
+        <v>4</v>
+      </c>
+      <c r="T76" s="15">
+        <v>1593.2782611111024</v>
+      </c>
+      <c r="U76" s="15">
+        <v>0</v>
+      </c>
+      <c r="V76" s="13">
+        <v>0</v>
+      </c>
+      <c r="W76" s="15">
+        <v>0</v>
+      </c>
+      <c r="X76" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y76" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z76" s="13"/>
+      <c r="AA76" s="13"/>
+      <c r="AB76" s="18"/>
+      <c r="AC76" s="18"/>
+      <c r="AD76" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE76" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A77" s="10"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F77" s="13">
+        <v>1</v>
+      </c>
+      <c r="G77" s="14">
+        <v>9552</v>
+      </c>
+      <c r="H77" s="14">
+        <v>0</v>
+      </c>
+      <c r="I77" s="14">
+        <v>2388</v>
+      </c>
+      <c r="J77" s="14">
+        <v>2388</v>
+      </c>
+      <c r="K77" s="13">
+        <v>1</v>
+      </c>
+      <c r="L77" s="13">
+        <v>1</v>
+      </c>
+      <c r="M77" s="14">
+        <v>4776</v>
+      </c>
+      <c r="N77" s="14">
+        <v>-4776</v>
+      </c>
+      <c r="O77" s="14">
+        <v>8</v>
+      </c>
+      <c r="P77" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q77" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R77" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S77" s="15">
+        <v>4</v>
+      </c>
+      <c r="T77" s="15">
+        <v>39427.445466666446</v>
+      </c>
+      <c r="U77" s="15">
+        <v>0</v>
+      </c>
+      <c r="V77" s="13">
+        <v>0</v>
+      </c>
+      <c r="W77" s="15">
+        <v>0</v>
+      </c>
+      <c r="X77" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y77" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z77" s="13"/>
+      <c r="AA77" s="13"/>
+      <c r="AB77" s="18"/>
+      <c r="AC77" s="18"/>
+      <c r="AD77" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE77" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A78" s="10"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D78" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F78" s="13">
+        <v>1</v>
+      </c>
+      <c r="G78" s="14">
+        <v>14000</v>
+      </c>
+      <c r="H78" s="14">
+        <v>0</v>
+      </c>
+      <c r="I78" s="14">
+        <v>3500</v>
+      </c>
+      <c r="J78" s="14">
+        <v>3500</v>
+      </c>
+      <c r="K78" s="13">
+        <v>1</v>
+      </c>
+      <c r="L78" s="13">
+        <v>1</v>
+      </c>
+      <c r="M78" s="14">
+        <v>7000</v>
+      </c>
+      <c r="N78" s="14">
+        <v>-7000</v>
+      </c>
+      <c r="O78" s="14">
+        <v>8</v>
+      </c>
+      <c r="P78" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q78" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R78" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S78" s="15">
+        <v>4</v>
+      </c>
+      <c r="T78" s="15">
+        <v>57787.294444444124</v>
+      </c>
+      <c r="U78" s="15">
+        <v>0</v>
+      </c>
+      <c r="V78" s="13">
+        <v>0</v>
+      </c>
+      <c r="W78" s="15">
+        <v>0</v>
+      </c>
+      <c r="X78" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y78" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z78" s="13"/>
+      <c r="AA78" s="13"/>
+      <c r="AB78" s="18"/>
+      <c r="AC78" s="18"/>
+      <c r="AD78" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE78" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A79" s="10"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F79" s="13">
+        <v>1</v>
+      </c>
+      <c r="G79" s="14">
+        <v>5</v>
+      </c>
+      <c r="H79" s="14">
+        <v>0</v>
+      </c>
+      <c r="I79" s="14">
+        <v>1.25</v>
+      </c>
+      <c r="J79" s="14">
+        <v>1.25</v>
+      </c>
+      <c r="K79" s="13">
+        <v>1</v>
+      </c>
+      <c r="L79" s="13">
+        <v>1</v>
+      </c>
+      <c r="M79" s="14">
+        <v>2.5</v>
+      </c>
+      <c r="N79" s="14">
+        <v>-2.5</v>
+      </c>
+      <c r="O79" s="14">
+        <v>8</v>
+      </c>
+      <c r="P79" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q79" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R79" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S79" s="15">
+        <v>4</v>
+      </c>
+      <c r="T79" s="15">
+        <v>20.638319444444331</v>
+      </c>
+      <c r="U79" s="15">
+        <v>0</v>
+      </c>
+      <c r="V79" s="13">
+        <v>0</v>
+      </c>
+      <c r="W79" s="15">
+        <v>0</v>
+      </c>
+      <c r="X79" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y79" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z79" s="13"/>
+      <c r="AA79" s="13"/>
+      <c r="AB79" s="18"/>
+      <c r="AC79" s="18"/>
+      <c r="AD79" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE79" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A80" s="10"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="D80" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F80" s="13">
+        <v>1</v>
+      </c>
+      <c r="G80" s="14">
+        <v>2302.83</v>
+      </c>
+      <c r="H80" s="14">
+        <v>0</v>
+      </c>
+      <c r="I80" s="14">
+        <v>575.70799999999997</v>
+      </c>
+      <c r="J80" s="14">
+        <v>575.70799999999997</v>
+      </c>
+      <c r="K80" s="13">
+        <v>1</v>
+      </c>
+      <c r="L80" s="13">
+        <v>1</v>
+      </c>
+      <c r="M80" s="14">
+        <v>1151.415</v>
+      </c>
+      <c r="N80" s="14">
+        <v>-1151.415</v>
+      </c>
+      <c r="O80" s="14">
+        <v>8</v>
+      </c>
+      <c r="P80" s="15">
+        <v>34.402025897080797</v>
+      </c>
+      <c r="Q80" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R80" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S80" s="15">
+        <v>4</v>
+      </c>
+      <c r="T80" s="15">
+        <v>9505.3082332499471</v>
+      </c>
+      <c r="U80" s="15">
+        <v>0</v>
+      </c>
+      <c r="V80" s="13">
+        <v>0</v>
+      </c>
+      <c r="W80" s="15">
+        <v>0</v>
+      </c>
+      <c r="X80" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y80" s="17">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="Z80" s="13"/>
+      <c r="AA80" s="13"/>
+      <c r="AB80" s="18"/>
+      <c r="AC80" s="18"/>
+      <c r="AD80" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE80" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A81" s="10"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="F81" s="13">
+        <v>1</v>
+      </c>
+      <c r="G81" s="14">
+        <v>2137.6</v>
+      </c>
+      <c r="H81" s="14">
+        <v>0</v>
+      </c>
+      <c r="I81" s="14">
+        <v>534.4</v>
+      </c>
+      <c r="J81" s="14">
+        <v>534.4</v>
+      </c>
+      <c r="K81" s="13">
+        <v>1</v>
+      </c>
+      <c r="L81" s="13">
+        <v>1</v>
+      </c>
+      <c r="M81" s="14">
+        <v>1068.8</v>
+      </c>
+      <c r="N81" s="14">
+        <v>-1068.8</v>
+      </c>
+      <c r="O81" s="14">
+        <v>8</v>
+      </c>
+      <c r="P81" s="15">
+        <v>1.72010129485404</v>
+      </c>
+      <c r="Q81" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R81" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S81" s="15">
+        <v>4</v>
+      </c>
+      <c r="T81" s="15">
+        <v>34796.090311110915</v>
+      </c>
+      <c r="U81" s="15">
+        <v>0</v>
+      </c>
+      <c r="V81" s="13">
+        <v>0</v>
+      </c>
+      <c r="W81" s="15">
+        <v>0</v>
+      </c>
+      <c r="X81" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y81" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="13"/>
+      <c r="AA81" s="13"/>
+      <c r="AB81" s="18"/>
+      <c r="AC81" s="18"/>
+      <c r="AD81" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE81" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A82" s="10"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D82" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="F82" s="13">
+        <v>1</v>
+      </c>
+      <c r="G82" s="14">
+        <v>36073.000008000003</v>
+      </c>
+      <c r="H82" s="14">
+        <v>0</v>
+      </c>
+      <c r="I82" s="14">
+        <v>9018.25</v>
+      </c>
+      <c r="J82" s="14">
+        <v>9018.25</v>
+      </c>
+      <c r="K82" s="13">
+        <v>1</v>
+      </c>
+      <c r="L82" s="13">
+        <v>1</v>
+      </c>
+      <c r="M82" s="14">
+        <v>18036.5</v>
+      </c>
+      <c r="N82" s="14">
+        <v>-18036.5</v>
+      </c>
+      <c r="O82" s="14">
+        <v>8</v>
+      </c>
+      <c r="P82" s="15">
+        <v>1.72010129485404</v>
+      </c>
+      <c r="Q82" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R82" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S82" s="15">
+        <v>4</v>
+      </c>
+      <c r="T82" s="15">
+        <v>587200.30224133283</v>
+      </c>
+      <c r="U82" s="15">
+        <v>0</v>
+      </c>
+      <c r="V82" s="13">
+        <v>0</v>
+      </c>
+      <c r="W82" s="15">
+        <v>0</v>
+      </c>
+      <c r="X82" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y82" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="13"/>
+      <c r="AA82" s="13"/>
+      <c r="AB82" s="18"/>
+      <c r="AC82" s="18"/>
+      <c r="AD82" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE82" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="83" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A83" s="10"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="F83" s="13">
+        <v>1</v>
+      </c>
+      <c r="G83" s="14">
+        <v>1300</v>
+      </c>
+      <c r="H83" s="14">
+        <v>0</v>
+      </c>
+      <c r="I83" s="14">
+        <v>325</v>
+      </c>
+      <c r="J83" s="14">
+        <v>325</v>
+      </c>
+      <c r="K83" s="13">
+        <v>1</v>
+      </c>
+      <c r="L83" s="13">
+        <v>1</v>
+      </c>
+      <c r="M83" s="14">
+        <v>650</v>
+      </c>
+      <c r="N83" s="14">
+        <v>-650</v>
+      </c>
+      <c r="O83" s="14">
+        <v>8</v>
+      </c>
+      <c r="P83" s="15">
+        <v>1.72010129485404</v>
+      </c>
+      <c r="Q83" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R83" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S83" s="15">
+        <v>4</v>
+      </c>
+      <c r="T83" s="15">
+        <v>21161.544444444327</v>
+      </c>
+      <c r="U83" s="15">
+        <v>0</v>
+      </c>
+      <c r="V83" s="13">
+        <v>0</v>
+      </c>
+      <c r="W83" s="15">
+        <v>0</v>
+      </c>
+      <c r="X83" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y83" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z83" s="13"/>
+      <c r="AA83" s="13"/>
+      <c r="AB83" s="18"/>
+      <c r="AC83" s="18"/>
+      <c r="AD83" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE83" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A84" s="10"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="D84" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="F84" s="13">
+        <v>1</v>
+      </c>
+      <c r="G84" s="14">
+        <v>703</v>
+      </c>
+      <c r="H84" s="14">
+        <v>0</v>
+      </c>
+      <c r="I84" s="14">
+        <v>175.75</v>
+      </c>
+      <c r="J84" s="14">
+        <v>175.75</v>
+      </c>
+      <c r="K84" s="13">
+        <v>1</v>
+      </c>
+      <c r="L84" s="13">
+        <v>1</v>
+      </c>
+      <c r="M84" s="14">
+        <v>351.5</v>
+      </c>
+      <c r="N84" s="14">
+        <v>-351.5</v>
+      </c>
+      <c r="O84" s="14">
+        <v>8</v>
+      </c>
+      <c r="P84" s="15">
+        <v>1.72010129485404</v>
+      </c>
+      <c r="Q84" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R84" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S84" s="15">
+        <v>4</v>
+      </c>
+      <c r="T84" s="15">
+        <v>11443.512111111047</v>
+      </c>
+      <c r="U84" s="15">
+        <v>0</v>
+      </c>
+      <c r="V84" s="13">
+        <v>0</v>
+      </c>
+      <c r="W84" s="15">
+        <v>0</v>
+      </c>
+      <c r="X84" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y84" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="13"/>
+      <c r="AA84" s="13"/>
+      <c r="AB84" s="18"/>
+      <c r="AC84" s="18"/>
+      <c r="AD84" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE84" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A85" s="10"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F85" s="13">
+        <v>1</v>
+      </c>
+      <c r="G85" s="14">
+        <v>2674.0000002000002</v>
+      </c>
+      <c r="H85" s="14">
+        <v>0</v>
+      </c>
+      <c r="I85" s="14">
+        <v>668.5</v>
+      </c>
+      <c r="J85" s="14">
+        <v>668.5</v>
+      </c>
+      <c r="K85" s="13">
+        <v>1</v>
+      </c>
+      <c r="L85" s="13">
+        <v>1</v>
+      </c>
+      <c r="M85" s="14">
+        <v>1337</v>
+      </c>
+      <c r="N85" s="14">
+        <v>-1337</v>
+      </c>
+      <c r="O85" s="14">
+        <v>8</v>
+      </c>
+      <c r="P85" s="15">
+        <v>1.72010129485404</v>
+      </c>
+      <c r="Q85" s="15">
+        <v>0.33001943447780996</v>
+      </c>
+      <c r="R85" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S85" s="15">
+        <v>4</v>
+      </c>
+      <c r="T85" s="15">
+        <v>43527.669114366487</v>
+      </c>
+      <c r="U85" s="15">
+        <v>0</v>
+      </c>
+      <c r="V85" s="13">
+        <v>0</v>
+      </c>
+      <c r="W85" s="15">
+        <v>0</v>
+      </c>
+      <c r="X85" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y85" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z85" s="13"/>
+      <c r="AA85" s="13"/>
+      <c r="AB85" s="18"/>
+      <c r="AC85" s="18"/>
+      <c r="AD85" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE85" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="86" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A86" s="10"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="D86" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="F86" s="13">
+        <v>1</v>
+      </c>
+      <c r="G86" s="14">
+        <v>354.4</v>
+      </c>
+      <c r="H86" s="14">
+        <v>0</v>
+      </c>
+      <c r="I86" s="14">
+        <v>88.6</v>
+      </c>
+      <c r="J86" s="14">
+        <v>88.6</v>
+      </c>
+      <c r="K86" s="13">
+        <v>1</v>
+      </c>
+      <c r="L86" s="13">
+        <v>1</v>
+      </c>
+      <c r="M86" s="14">
+        <v>177.2</v>
+      </c>
+      <c r="N86" s="14">
+        <v>-177.2</v>
+      </c>
+      <c r="O86" s="14">
+        <v>8</v>
+      </c>
+      <c r="P86" s="15">
+        <v>61.063595967318413</v>
+      </c>
+      <c r="Q86" s="15">
+        <v>0.43002532371350993</v>
+      </c>
+      <c r="R86" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S86" s="15">
+        <v>4</v>
+      </c>
+      <c r="T86" s="15">
+        <v>446.89146729264235</v>
+      </c>
+      <c r="U86" s="15">
+        <v>0</v>
+      </c>
+      <c r="V86" s="13">
+        <v>0</v>
+      </c>
+      <c r="W86" s="15">
+        <v>0</v>
+      </c>
+      <c r="X86" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y86" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z86" s="13"/>
+      <c r="AA86" s="13"/>
+      <c r="AB86" s="18"/>
+      <c r="AC86" s="18"/>
+      <c r="AD86" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE86" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="87" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A87" s="10"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="F87" s="13">
+        <v>1</v>
+      </c>
+      <c r="G87" s="14">
+        <v>975.71750000333429</v>
+      </c>
+      <c r="H87" s="14">
+        <v>0</v>
+      </c>
+      <c r="I87" s="14">
+        <v>243.929</v>
+      </c>
+      <c r="J87" s="14">
+        <v>243.929</v>
+      </c>
+      <c r="K87" s="13">
+        <v>1</v>
+      </c>
+      <c r="L87" s="13">
+        <v>1</v>
+      </c>
+      <c r="M87" s="14">
+        <v>487.85899999999998</v>
+      </c>
+      <c r="N87" s="14">
+        <v>-487.85899999999998</v>
+      </c>
+      <c r="O87" s="14">
+        <v>8</v>
+      </c>
+      <c r="P87" s="15">
+        <v>61.063595967318413</v>
+      </c>
+      <c r="Q87" s="15">
+        <v>0.43002532371350993</v>
+      </c>
+      <c r="R87" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S87" s="15">
+        <v>4</v>
+      </c>
+      <c r="T87" s="15">
+        <v>1230.3606806986422</v>
+      </c>
+      <c r="U87" s="15">
+        <v>0</v>
+      </c>
+      <c r="V87" s="13">
+        <v>0</v>
+      </c>
+      <c r="W87" s="15">
+        <v>0</v>
+      </c>
+      <c r="X87" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y87" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z87" s="13"/>
+      <c r="AA87" s="13"/>
+      <c r="AB87" s="18"/>
+      <c r="AC87" s="18"/>
+      <c r="AD87" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE87" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A88" s="10"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D88" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="F88" s="13">
+        <v>1</v>
+      </c>
+      <c r="G88" s="14">
+        <v>435.2033333333344</v>
+      </c>
+      <c r="H88" s="14">
+        <v>0</v>
+      </c>
+      <c r="I88" s="14">
+        <v>108.801</v>
+      </c>
+      <c r="J88" s="14">
+        <v>108.801</v>
+      </c>
+      <c r="K88" s="13">
+        <v>1</v>
+      </c>
+      <c r="L88" s="13">
+        <v>1</v>
+      </c>
+      <c r="M88" s="14">
+        <v>217.602</v>
+      </c>
+      <c r="N88" s="14">
+        <v>-217.602</v>
+      </c>
+      <c r="O88" s="14">
+        <v>8</v>
+      </c>
+      <c r="P88" s="15">
+        <v>61.063595967318413</v>
+      </c>
+      <c r="Q88" s="15">
+        <v>0.43002532371350993</v>
+      </c>
+      <c r="R88" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S88" s="15">
+        <v>4</v>
+      </c>
+      <c r="T88" s="15">
+        <v>548.78288996609126</v>
+      </c>
+      <c r="U88" s="15">
+        <v>0</v>
+      </c>
+      <c r="V88" s="13">
+        <v>0</v>
+      </c>
+      <c r="W88" s="15">
+        <v>0</v>
+      </c>
+      <c r="X88" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y88" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z88" s="13"/>
+      <c r="AA88" s="13"/>
+      <c r="AB88" s="18"/>
+      <c r="AC88" s="18"/>
+      <c r="AD88" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE88" s="19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="89" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A89" s="10"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="F89" s="13">
+        <v>1</v>
+      </c>
+      <c r="G89" s="14">
+        <v>217.78947579999979</v>
+      </c>
+      <c r="H89" s="14">
+        <v>0</v>
+      </c>
+      <c r="I89" s="14">
+        <v>54.447000000000003</v>
+      </c>
+      <c r="J89" s="14">
+        <v>54.447000000000003</v>
+      </c>
+      <c r="K89" s="13">
+        <v>1</v>
+      </c>
+      <c r="L89" s="13">
+        <v>1</v>
+      </c>
+      <c r="M89" s="14">
+        <v>108.895</v>
+      </c>
+      <c r="N89" s="14">
+        <v>-108.895</v>
+      </c>
+      <c r="O89" s="14">
+        <v>8</v>
+      </c>
+      <c r="P89" s="15">
+        <v>61.063595967318413</v>
+      </c>
+      <c r="Q89" s="15">
+        <v>0.43002532371350993</v>
+      </c>
+      <c r="R89" s="15">
+        <v>11.627222222222159</v>
+      </c>
+      <c r="S89" s="15">
+        <v>4</v>
+      </c>
+      <c r="T89" s="15">
+        <v>274.62826862629043</v>
+      </c>
+      <c r="U89" s="15">
+        <v>0</v>
+      </c>
+      <c r="V89" s="13">
+        <v>0</v>
+      </c>
+      <c r="W89" s="15">
+        <v>0</v>
+      </c>
+      <c r="X89" s="16">
+        <v>0.97</v>
+      </c>
+      <c r="Y89" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z89" s="13"/>
+      <c r="AA89" s="13"/>
+      <c r="AB89" s="18"/>
+      <c r="AC89" s="18"/>
+      <c r="AD89" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="AE89" s="19" t="s">
         <v>98</v>
       </c>
     </row>

--- a/data/hydroExample/Power_ThermalGen.xlsx
+++ b/data/hydroExample/Power_ThermalGen.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FelixAuer\Git\LEGO-Pyomo2\data\hydroExample\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E3797F0-22C4-4EBA-8C49-014EF1246937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04030C7D-99D0-4947-BF76-02474BD05F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4170" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34230" yWindow="-21705" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario_2016" sheetId="1" r:id="rId1"/>
@@ -1760,7 +1760,7 @@
         <v>100</v>
       </c>
       <c r="F8" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="14">
         <v>133</v>
@@ -1808,10 +1808,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X8" s="16">
         <v>0.97</v>
@@ -1843,7 +1843,7 @@
         <v>102</v>
       </c>
       <c r="F9" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14">
         <v>576</v>
@@ -1891,10 +1891,10 @@
         <v>0</v>
       </c>
       <c r="V9" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X9" s="16">
         <v>0.97</v>
@@ -1926,7 +1926,7 @@
         <v>104</v>
       </c>
       <c r="F10" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="14">
         <v>222</v>
@@ -1974,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="V10" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X10" s="16">
         <v>0.97</v>
@@ -2009,7 +2009,7 @@
         <v>106</v>
       </c>
       <c r="F11" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
         <v>238</v>
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="V11" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X11" s="16">
         <v>0.97</v>
@@ -2092,7 +2092,7 @@
         <v>108</v>
       </c>
       <c r="F12" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
         <v>7</v>
@@ -2140,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="V12" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X12" s="16">
         <v>0.97</v>
@@ -2175,7 +2175,7 @@
         <v>110</v>
       </c>
       <c r="F13" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="14">
         <v>200</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X13" s="16">
         <v>0.97</v>
@@ -2258,7 +2258,7 @@
         <v>112</v>
       </c>
       <c r="F14" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" s="14">
         <v>6164.3000002999997</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="V14" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W14" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X14" s="16">
         <v>0.97</v>
@@ -2341,7 +2341,7 @@
         <v>114</v>
       </c>
       <c r="F15" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14">
         <v>752</v>
@@ -2389,10 +2389,10 @@
         <v>0</v>
       </c>
       <c r="V15" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W15" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X15" s="16">
         <v>0.97</v>
@@ -2424,7 +2424,7 @@
         <v>116</v>
       </c>
       <c r="F16" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" s="14">
         <v>3205</v>
@@ -2472,10 +2472,10 @@
         <v>0</v>
       </c>
       <c r="V16" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X16" s="16">
         <v>0.97</v>
@@ -2507,7 +2507,7 @@
         <v>118</v>
       </c>
       <c r="F17" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
         <v>23332</v>
@@ -2555,10 +2555,10 @@
         <v>0</v>
       </c>
       <c r="V17" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X17" s="16">
         <v>0.97</v>
@@ -2590,7 +2590,7 @@
         <v>120</v>
       </c>
       <c r="F18" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14">
         <v>24498.560000000001</v>
@@ -2638,10 +2638,10 @@
         <v>0</v>
       </c>
       <c r="V18" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W18" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X18" s="16">
         <v>0.97</v>
@@ -2673,7 +2673,7 @@
         <v>122</v>
       </c>
       <c r="F19" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14">
         <v>6552.9999995999997</v>
@@ -2721,10 +2721,10 @@
         <v>0</v>
       </c>
       <c r="V19" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X19" s="16">
         <v>0.97</v>
@@ -2756,7 +2756,7 @@
         <v>124</v>
       </c>
       <c r="F20" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" s="14">
         <v>6347.1000002000001</v>
@@ -2804,10 +2804,10 @@
         <v>0</v>
       </c>
       <c r="V20" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W20" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X20" s="16">
         <v>0.97</v>
@@ -2839,7 +2839,7 @@
         <v>126</v>
       </c>
       <c r="F21" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="14">
         <v>380</v>
@@ -2887,10 +2887,10 @@
         <v>0</v>
       </c>
       <c r="V21" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W21" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X21" s="16">
         <v>0.97</v>
@@ -2922,7 +2922,7 @@
         <v>128</v>
       </c>
       <c r="F22" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="14">
         <v>1344</v>
@@ -2970,10 +2970,10 @@
         <v>0</v>
       </c>
       <c r="V22" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W22" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X22" s="16">
         <v>0.97</v>
@@ -3005,7 +3005,7 @@
         <v>130</v>
       </c>
       <c r="F23" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="14">
         <v>33812.799999199997</v>
@@ -3053,10 +3053,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X23" s="16">
         <v>0.97</v>
@@ -3088,7 +3088,7 @@
         <v>132</v>
       </c>
       <c r="F24" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="14">
         <v>17598</v>
@@ -3136,10 +3136,10 @@
         <v>0</v>
       </c>
       <c r="V24" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X24" s="16">
         <v>0.97</v>
@@ -3171,7 +3171,7 @@
         <v>134</v>
       </c>
       <c r="F25" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="14">
         <v>7689.3000001999999</v>
@@ -3219,10 +3219,10 @@
         <v>0</v>
       </c>
       <c r="V25" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W25" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X25" s="16">
         <v>0.97</v>
@@ -3254,7 +3254,7 @@
         <v>136</v>
       </c>
       <c r="F26" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14">
         <v>2839.0000002000002</v>
@@ -3302,10 +3302,10 @@
         <v>0</v>
       </c>
       <c r="V26" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X26" s="16">
         <v>0.97</v>
@@ -3337,7 +3337,7 @@
         <v>138</v>
       </c>
       <c r="F27" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="14">
         <v>4006.3999994999999</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="V27" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X27" s="16">
         <v>0.97</v>
@@ -3420,7 +3420,7 @@
         <v>140</v>
       </c>
       <c r="F28" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" s="14">
         <v>182.90000001000001</v>
@@ -3468,10 +3468,10 @@
         <v>0</v>
       </c>
       <c r="V28" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X28" s="16">
         <v>0.97</v>
@@ -3503,7 +3503,7 @@
         <v>142</v>
       </c>
       <c r="F29" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14">
         <v>114</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="V29" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W29" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X29" s="16">
         <v>0.97</v>
@@ -3586,7 +3586,7 @@
         <v>144</v>
       </c>
       <c r="F30" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G30" s="14">
         <v>411.49</v>
@@ -3634,10 +3634,10 @@
         <v>0</v>
       </c>
       <c r="V30" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X30" s="16">
         <v>0.97</v>
@@ -3669,7 +3669,7 @@
         <v>110</v>
       </c>
       <c r="F31" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G31" s="14">
         <v>100</v>
@@ -3717,10 +3717,10 @@
         <v>0</v>
       </c>
       <c r="V31" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W31" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X31" s="16">
         <v>0.97</v>
@@ -3752,7 +3752,7 @@
         <v>112</v>
       </c>
       <c r="F32" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14">
         <v>950.3</v>
@@ -3800,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W32" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X32" s="16">
         <v>0.97</v>
@@ -3835,7 +3835,7 @@
         <v>116</v>
       </c>
       <c r="F33" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14">
         <v>509.4</v>
@@ -3883,10 +3883,10 @@
         <v>0</v>
       </c>
       <c r="V33" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X33" s="16">
         <v>0.97</v>
@@ -3918,7 +3918,7 @@
         <v>118</v>
       </c>
       <c r="F34" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G34" s="14">
         <v>8086.8590008000001</v>
@@ -3966,10 +3966,10 @@
         <v>0</v>
       </c>
       <c r="V34" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X34" s="16">
         <v>0.97</v>
@@ -4001,7 +4001,7 @@
         <v>150</v>
       </c>
       <c r="F35" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="14">
         <v>138.5</v>
@@ -4049,10 +4049,10 @@
         <v>0</v>
       </c>
       <c r="V35" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X35" s="16">
         <v>0.97</v>
@@ -4084,7 +4084,7 @@
         <v>152</v>
       </c>
       <c r="F36" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="14">
         <v>195.55</v>
@@ -4132,10 +4132,10 @@
         <v>0</v>
       </c>
       <c r="V36" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X36" s="16">
         <v>0.97</v>
@@ -4167,7 +4167,7 @@
         <v>124</v>
       </c>
       <c r="F37" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="14">
         <v>476.3</v>
@@ -4215,10 +4215,10 @@
         <v>0</v>
       </c>
       <c r="V37" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W37" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X37" s="16">
         <v>0.97</v>
@@ -4250,7 +4250,7 @@
         <v>128</v>
       </c>
       <c r="F38" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="14">
         <v>102</v>
@@ -4298,10 +4298,10 @@
         <v>0</v>
       </c>
       <c r="V38" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X38" s="16">
         <v>0.97</v>
@@ -4333,7 +4333,7 @@
         <v>130</v>
       </c>
       <c r="F39" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14">
         <v>1600.9999998000001</v>
@@ -4381,10 +4381,10 @@
         <v>0</v>
       </c>
       <c r="V39" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W39" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X39" s="16">
         <v>0.97</v>
@@ -4416,7 +4416,7 @@
         <v>132</v>
       </c>
       <c r="F40" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14">
         <v>3983.4999994999998</v>
@@ -4464,10 +4464,10 @@
         <v>0</v>
       </c>
       <c r="V40" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X40" s="16">
         <v>0.97</v>
@@ -4499,7 +4499,7 @@
         <v>144</v>
       </c>
       <c r="F41" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G41" s="14">
         <v>213.64999999999989</v>
@@ -4547,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="V41" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X41" s="16">
         <v>0.97</v>
@@ -4582,7 +4582,7 @@
         <v>112</v>
       </c>
       <c r="F42" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="14">
         <v>878</v>
@@ -4630,10 +4630,10 @@
         <v>0</v>
       </c>
       <c r="V42" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W42" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X42" s="16">
         <v>0.97</v>
@@ -4665,7 +4665,7 @@
         <v>114</v>
       </c>
       <c r="F43" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" s="14">
         <v>1120.9999999900001</v>
@@ -4713,10 +4713,10 @@
         <v>0</v>
       </c>
       <c r="V43" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W43" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X43" s="16">
         <v>0.97</v>
@@ -4748,7 +4748,7 @@
         <v>118</v>
       </c>
       <c r="F44" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G44" s="14">
         <v>1724.69999998</v>
@@ -4796,10 +4796,10 @@
         <v>0</v>
       </c>
       <c r="V44" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W44" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X44" s="16">
         <v>0.97</v>
@@ -4831,7 +4831,7 @@
         <v>150</v>
       </c>
       <c r="F45" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G45" s="14">
         <v>7.8866666666666596</v>
@@ -4879,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="V45" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W45" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X45" s="16">
         <v>0.97</v>
@@ -4914,7 +4914,7 @@
         <v>152</v>
       </c>
       <c r="F46" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="14">
         <v>41.16</v>
@@ -4962,10 +4962,10 @@
         <v>0</v>
       </c>
       <c r="V46" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W46" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X46" s="16">
         <v>0.97</v>
@@ -4997,7 +4997,7 @@
         <v>122</v>
       </c>
       <c r="F47" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" s="14">
         <v>199</v>
@@ -5045,10 +5045,10 @@
         <v>0</v>
       </c>
       <c r="V47" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W47" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X47" s="16">
         <v>0.97</v>
@@ -5080,7 +5080,7 @@
         <v>124</v>
       </c>
       <c r="F48" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="14">
         <v>147.762</v>
@@ -5128,10 +5128,10 @@
         <v>0</v>
       </c>
       <c r="V48" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X48" s="16">
         <v>0.97</v>
@@ -5163,7 +5163,7 @@
         <v>128</v>
       </c>
       <c r="F49" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G49" s="14">
         <v>156</v>
@@ -5211,10 +5211,10 @@
         <v>0</v>
       </c>
       <c r="V49" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W49" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X49" s="16">
         <v>0.97</v>
@@ -5246,7 +5246,7 @@
         <v>130</v>
       </c>
       <c r="F50" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G50" s="14">
         <v>690.00000009999985</v>
@@ -5294,10 +5294,10 @@
         <v>0</v>
       </c>
       <c r="V50" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W50" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X50" s="16">
         <v>0.97</v>
@@ -5329,7 +5329,7 @@
         <v>132</v>
       </c>
       <c r="F51" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="14">
         <v>233.00000003</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="V51" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X51" s="16">
         <v>0.97</v>
@@ -5412,7 +5412,7 @@
         <v>138</v>
       </c>
       <c r="F52" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G52" s="14">
         <v>531.202</v>
@@ -5460,10 +5460,10 @@
         <v>0</v>
       </c>
       <c r="V52" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X52" s="16">
         <v>0.97</v>
@@ -5495,7 +5495,7 @@
         <v>140</v>
       </c>
       <c r="F53" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G53" s="14">
         <v>218</v>
@@ -5543,10 +5543,10 @@
         <v>0</v>
       </c>
       <c r="V53" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W53" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X53" s="16">
         <v>0.97</v>
@@ -5578,7 +5578,7 @@
         <v>142</v>
       </c>
       <c r="F54" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="14">
         <v>331</v>
@@ -5626,10 +5626,10 @@
         <v>0</v>
       </c>
       <c r="V54" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W54" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X54" s="16">
         <v>0.97</v>
@@ -5661,7 +5661,7 @@
         <v>144</v>
       </c>
       <c r="F55" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G55" s="14">
         <v>90.11</v>
@@ -5709,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="V55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W55" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X55" s="16">
         <v>0.97</v>
@@ -5744,7 +5744,7 @@
         <v>112</v>
       </c>
       <c r="F56" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="14">
         <v>244</v>
@@ -5792,10 +5792,10 @@
         <v>0</v>
       </c>
       <c r="V56" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X56" s="16">
         <v>0.97</v>
@@ -5827,7 +5827,7 @@
         <v>114</v>
       </c>
       <c r="F57" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="14">
         <v>20</v>
@@ -5875,10 +5875,10 @@
         <v>0</v>
       </c>
       <c r="V57" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W57" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X57" s="16">
         <v>0.97</v>
@@ -5910,7 +5910,7 @@
         <v>118</v>
       </c>
       <c r="F58" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="14">
         <v>3831</v>
@@ -5958,10 +5958,10 @@
         <v>0</v>
       </c>
       <c r="V58" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W58" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X58" s="16">
         <v>0.97</v>
@@ -5993,7 +5993,7 @@
         <v>150</v>
       </c>
       <c r="F59" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="14">
         <v>88.508333350000001</v>
@@ -6041,10 +6041,10 @@
         <v>0</v>
       </c>
       <c r="V59" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X59" s="16">
         <v>0.97</v>
@@ -6076,7 +6076,7 @@
         <v>152</v>
       </c>
       <c r="F60" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" s="14">
         <v>13.9266666666667</v>
@@ -6124,10 +6124,10 @@
         <v>0</v>
       </c>
       <c r="V60" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X60" s="16">
         <v>0.97</v>
@@ -6159,7 +6159,7 @@
         <v>122</v>
       </c>
       <c r="F61" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="14">
         <v>437.00000010000002</v>
@@ -6207,10 +6207,10 @@
         <v>0</v>
       </c>
       <c r="V61" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W61" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X61" s="16">
         <v>0.97</v>
@@ -6242,7 +6242,7 @@
         <v>130</v>
       </c>
       <c r="F62" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G62" s="14">
         <v>3130</v>
@@ -6290,10 +6290,10 @@
         <v>0</v>
       </c>
       <c r="V62" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X62" s="16">
         <v>0.97</v>
@@ -6325,7 +6325,7 @@
         <v>132</v>
       </c>
       <c r="F63" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G63" s="14">
         <v>547.80000013999995</v>
@@ -6373,10 +6373,10 @@
         <v>0</v>
       </c>
       <c r="V63" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X63" s="16">
         <v>0.97</v>
@@ -6408,7 +6408,7 @@
         <v>134</v>
       </c>
       <c r="F64" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="14">
         <v>3600</v>
@@ -6456,10 +6456,10 @@
         <v>0</v>
       </c>
       <c r="V64" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W64" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X64" s="16">
         <v>0.97</v>
@@ -6491,7 +6491,7 @@
         <v>138</v>
       </c>
       <c r="F65" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G65" s="14">
         <v>1050.8999997999999</v>
@@ -6539,10 +6539,10 @@
         <v>0</v>
       </c>
       <c r="V65" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W65" s="15">
-        <v>0</v>
+        <v>36622.724776842995</v>
       </c>
       <c r="X65" s="16">
         <v>0.97</v>
@@ -6574,7 +6574,7 @@
         <v>112</v>
       </c>
       <c r="F66" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="14">
         <v>6488.99999999997</v>
@@ -6622,10 +6622,10 @@
         <v>0</v>
       </c>
       <c r="V66" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X66" s="16">
         <v>0.97</v>
@@ -6657,7 +6657,7 @@
         <v>114</v>
       </c>
       <c r="F67" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G67" s="14">
         <v>2296</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="V67" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X67" s="16">
         <v>0.97</v>
@@ -6740,7 +6740,7 @@
         <v>186</v>
       </c>
       <c r="F68" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="14">
         <v>1771</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="V68" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W68" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X68" s="16">
         <v>0.97</v>
@@ -6823,7 +6823,7 @@
         <v>116</v>
       </c>
       <c r="F69" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="14">
         <v>4454</v>
@@ -6871,10 +6871,10 @@
         <v>0</v>
       </c>
       <c r="V69" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X69" s="16">
         <v>0.97</v>
@@ -6906,7 +6906,7 @@
         <v>150</v>
       </c>
       <c r="F70" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="14">
         <v>2364.4675000000002</v>
@@ -6954,10 +6954,10 @@
         <v>0</v>
       </c>
       <c r="V70" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W70" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X70" s="16">
         <v>0.97</v>
@@ -6989,7 +6989,7 @@
         <v>152</v>
       </c>
       <c r="F71" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="14">
         <v>3229.0999999999899</v>
@@ -7037,10 +7037,10 @@
         <v>0</v>
       </c>
       <c r="V71" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W71" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X71" s="16">
         <v>0.97</v>
@@ -7072,7 +7072,7 @@
         <v>120</v>
       </c>
       <c r="F72" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="14">
         <v>377</v>
@@ -7120,10 +7120,10 @@
         <v>0</v>
       </c>
       <c r="V72" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W72" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X72" s="16">
         <v>0.97</v>
@@ -7155,7 +7155,7 @@
         <v>122</v>
       </c>
       <c r="F73" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="14">
         <v>16233</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="V73" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X73" s="16">
         <v>0.97</v>
@@ -7238,7 +7238,7 @@
         <v>128</v>
       </c>
       <c r="F74" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G74" s="14">
         <v>1806</v>
@@ -7286,10 +7286,10 @@
         <v>0</v>
       </c>
       <c r="V74" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W74" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X74" s="16">
         <v>0.97</v>
@@ -7321,7 +7321,7 @@
         <v>130</v>
       </c>
       <c r="F75" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="14">
         <v>219</v>
@@ -7369,10 +7369,10 @@
         <v>0</v>
       </c>
       <c r="V75" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X75" s="16">
         <v>0.97</v>
@@ -7404,7 +7404,7 @@
         <v>195</v>
       </c>
       <c r="F76" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" s="14">
         <v>386</v>
@@ -7452,10 +7452,10 @@
         <v>0</v>
       </c>
       <c r="V76" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X76" s="16">
         <v>0.97</v>
@@ -7487,7 +7487,7 @@
         <v>132</v>
       </c>
       <c r="F77" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="14">
         <v>9552</v>
@@ -7535,10 +7535,10 @@
         <v>0</v>
       </c>
       <c r="V77" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W77" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X77" s="16">
         <v>0.97</v>
@@ -7570,7 +7570,7 @@
         <v>134</v>
       </c>
       <c r="F78" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" s="14">
         <v>14000</v>
@@ -7618,10 +7618,10 @@
         <v>0</v>
       </c>
       <c r="V78" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W78" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X78" s="16">
         <v>0.97</v>
@@ -7653,7 +7653,7 @@
         <v>138</v>
       </c>
       <c r="F79" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79" s="14">
         <v>5</v>
@@ -7701,10 +7701,10 @@
         <v>0</v>
       </c>
       <c r="V79" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W79" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X79" s="16">
         <v>0.97</v>
@@ -7736,7 +7736,7 @@
         <v>144</v>
       </c>
       <c r="F80" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G80" s="14">
         <v>2302.83</v>
@@ -7784,10 +7784,10 @@
         <v>0</v>
       </c>
       <c r="V80" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="15">
-        <v>0</v>
+        <v>40193.086714605401</v>
       </c>
       <c r="X80" s="16">
         <v>0.97</v>
@@ -8234,7 +8234,7 @@
         <v>112</v>
       </c>
       <c r="F86" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" s="14">
         <v>354.4</v>
@@ -8282,10 +8282,10 @@
         <v>0</v>
       </c>
       <c r="V86" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W86" s="15">
-        <v>0</v>
+        <v>185597.01936204784</v>
       </c>
       <c r="X86" s="16">
         <v>0.97</v>
@@ -8317,7 +8317,7 @@
         <v>150</v>
       </c>
       <c r="F87" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87" s="14">
         <v>975.71750000333429</v>
@@ -8365,10 +8365,10 @@
         <v>0</v>
       </c>
       <c r="V87" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W87" s="15">
-        <v>0</v>
+        <v>185597.01936204784</v>
       </c>
       <c r="X87" s="16">
         <v>0.97</v>
@@ -8400,7 +8400,7 @@
         <v>152</v>
       </c>
       <c r="F88" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G88" s="14">
         <v>435.2033333333344</v>
@@ -8448,10 +8448,10 @@
         <v>0</v>
       </c>
       <c r="V88" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W88" s="15">
-        <v>0</v>
+        <v>185597.01936204784</v>
       </c>
       <c r="X88" s="16">
         <v>0.97</v>
@@ -8483,7 +8483,7 @@
         <v>144</v>
       </c>
       <c r="F89" s="13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G89" s="14">
         <v>217.78947579999979</v>
@@ -8531,10 +8531,10 @@
         <v>0</v>
       </c>
       <c r="V89" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W89" s="15">
-        <v>0</v>
+        <v>185597.01936204784</v>
       </c>
       <c r="X89" s="16">
         <v>0.97</v>
